--- a/development/one_file_rosetta_output/SP67609_rosetta.xlsx
+++ b/development/one_file_rosetta_output/SP67609_rosetta.xlsx
@@ -398,14 +398,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:E696"/>
+  <dimension ref="A1:F696"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
     <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
     <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="70.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="7.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="70.711"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -426,10 +427,15 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
+          <t>N indels</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
           <t>Example n</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Indel in context</t>
         </is>
@@ -452,9 +458,12 @@
         </is>
       </c>
       <c r="D2" s="4">
+        <v>8</v>
+      </c>
+      <c r="E2" s="4">
         <v>1</v>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -508,9 +517,12 @@
         </is>
       </c>
       <c r="D3" s="4">
+        <v>8</v>
+      </c>
+      <c r="E3" s="4">
         <v>2</v>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -564,9 +576,12 @@
         </is>
       </c>
       <c r="D4" s="4">
+        <v>8</v>
+      </c>
+      <c r="E4" s="4">
         <v>3</v>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -620,9 +635,12 @@
         </is>
       </c>
       <c r="D5" s="4">
+        <v>8</v>
+      </c>
+      <c r="E5" s="4">
         <v>4</v>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -676,9 +694,12 @@
         </is>
       </c>
       <c r="D6" s="4">
+        <v>8</v>
+      </c>
+      <c r="E6" s="4">
         <v>5</v>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -734,7 +755,10 @@
       <c r="D7" s="4">
         <v>1</v>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="4">
+        <v>1</v>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -788,9 +812,12 @@
         </is>
       </c>
       <c r="D8" s="4">
+        <v>12</v>
+      </c>
+      <c r="E8" s="4">
         <v>1</v>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -844,9 +871,12 @@
         </is>
       </c>
       <c r="D9" s="4">
+        <v>12</v>
+      </c>
+      <c r="E9" s="4">
         <v>2</v>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -900,9 +930,12 @@
         </is>
       </c>
       <c r="D10" s="4">
+        <v>12</v>
+      </c>
+      <c r="E10" s="4">
         <v>3</v>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -956,9 +989,12 @@
         </is>
       </c>
       <c r="D11" s="4">
+        <v>12</v>
+      </c>
+      <c r="E11" s="4">
         <v>4</v>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1012,9 +1048,12 @@
         </is>
       </c>
       <c r="D12" s="4">
+        <v>12</v>
+      </c>
+      <c r="E12" s="4">
         <v>5</v>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1068,9 +1107,12 @@
         </is>
       </c>
       <c r="D13" s="4">
+        <v>3</v>
+      </c>
+      <c r="E13" s="4">
         <v>1</v>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1131,9 +1173,12 @@
         </is>
       </c>
       <c r="D14" s="4">
+        <v>3</v>
+      </c>
+      <c r="E14" s="4">
         <v>1</v>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1194,9 +1239,12 @@
         </is>
       </c>
       <c r="D15" s="4">
+        <v>3</v>
+      </c>
+      <c r="E15" s="4">
         <v>2</v>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1257,9 +1305,12 @@
         </is>
       </c>
       <c r="D16" s="4">
+        <v>3</v>
+      </c>
+      <c r="E16" s="4">
         <v>1</v>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="F16" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1328,9 +1379,12 @@
         </is>
       </c>
       <c r="D17" s="4">
+        <v>2</v>
+      </c>
+      <c r="E17" s="4">
         <v>1</v>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="F17" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1401,7 +1455,10 @@
       <c r="D18" s="4">
         <v>2</v>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E18" s="4">
+        <v>2</v>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1472,7 +1529,10 @@
       <c r="D19" s="4">
         <v>1</v>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="E19" s="4">
+        <v>1</v>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1550,7 +1610,10 @@
       <c r="D20" s="4">
         <v>1</v>
       </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="E20" s="4">
+        <v>1</v>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1626,9 +1689,12 @@
         </is>
       </c>
       <c r="D21" s="4">
+        <v>3</v>
+      </c>
+      <c r="E21" s="4">
         <v>1</v>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="F21" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -1654,9 +1720,12 @@
         </is>
       </c>
       <c r="D22" s="4">
+        <v>2</v>
+      </c>
+      <c r="E22" s="4">
         <v>1</v>
       </c>
-      <c r="E22" s="6" t="inlineStr">
+      <c r="F22" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -1682,9 +1751,12 @@
         </is>
       </c>
       <c r="D23" s="4">
+        <v>2</v>
+      </c>
+      <c r="E23" s="4">
         <v>1</v>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="F23" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1740,7 +1812,10 @@
       <c r="D24" s="4">
         <v>1</v>
       </c>
-      <c r="E24" s="6" t="inlineStr">
+      <c r="E24" s="4">
+        <v>1</v>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -1766,9 +1841,12 @@
         </is>
       </c>
       <c r="D25" s="4">
+        <v>11</v>
+      </c>
+      <c r="E25" s="4">
         <v>1</v>
       </c>
-      <c r="E25" s="6" t="inlineStr">
+      <c r="F25" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1822,9 +1900,12 @@
         </is>
       </c>
       <c r="D26" s="4">
+        <v>11</v>
+      </c>
+      <c r="E26" s="4">
         <v>2</v>
       </c>
-      <c r="E26" s="6" t="inlineStr">
+      <c r="F26" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1878,9 +1959,12 @@
         </is>
       </c>
       <c r="D27" s="4">
+        <v>11</v>
+      </c>
+      <c r="E27" s="4">
         <v>3</v>
       </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="F27" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1934,9 +2018,12 @@
         </is>
       </c>
       <c r="D28" s="4">
+        <v>11</v>
+      </c>
+      <c r="E28" s="4">
         <v>4</v>
       </c>
-      <c r="E28" s="6" t="inlineStr">
+      <c r="F28" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1990,9 +2077,12 @@
         </is>
       </c>
       <c r="D29" s="4">
+        <v>11</v>
+      </c>
+      <c r="E29" s="4">
         <v>5</v>
       </c>
-      <c r="E29" s="6" t="inlineStr">
+      <c r="F29" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2046,9 +2136,12 @@
         </is>
       </c>
       <c r="D30" s="4">
+        <v>4</v>
+      </c>
+      <c r="E30" s="4">
         <v>1</v>
       </c>
-      <c r="E30" s="6" t="inlineStr">
+      <c r="F30" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2109,9 +2202,12 @@
         </is>
       </c>
       <c r="D31" s="4">
+        <v>3</v>
+      </c>
+      <c r="E31" s="4">
         <v>1</v>
       </c>
-      <c r="E31" s="6" t="inlineStr">
+      <c r="F31" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2172,9 +2268,12 @@
         </is>
       </c>
       <c r="D32" s="4">
+        <v>3</v>
+      </c>
+      <c r="E32" s="4">
         <v>2</v>
       </c>
-      <c r="E32" s="6" t="inlineStr">
+      <c r="F32" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2235,9 +2334,12 @@
         </is>
       </c>
       <c r="D33" s="4">
+        <v>2</v>
+      </c>
+      <c r="E33" s="4">
         <v>1</v>
       </c>
-      <c r="E33" s="6" t="inlineStr">
+      <c r="F33" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2306,9 +2408,12 @@
         </is>
       </c>
       <c r="D34" s="4">
+        <v>3</v>
+      </c>
+      <c r="E34" s="4">
         <v>1</v>
       </c>
-      <c r="E34" s="6" t="inlineStr">
+      <c r="F34" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2377,9 +2482,12 @@
         </is>
       </c>
       <c r="D35" s="4">
+        <v>3</v>
+      </c>
+      <c r="E35" s="4">
         <v>2</v>
       </c>
-      <c r="E35" s="6" t="inlineStr">
+      <c r="F35" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2448,9 +2556,12 @@
         </is>
       </c>
       <c r="D36" s="4">
+        <v>2</v>
+      </c>
+      <c r="E36" s="4">
         <v>1</v>
       </c>
-      <c r="E36" s="6" t="inlineStr">
+      <c r="F36" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -2478,7 +2589,10 @@
       <c r="D37" s="4">
         <v>1</v>
       </c>
-      <c r="E37" s="6" t="inlineStr">
+      <c r="E37" s="4">
+        <v>1</v>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2556,7 +2670,10 @@
       <c r="D38" s="4">
         <v>1</v>
       </c>
-      <c r="E38" s="6" t="inlineStr">
+      <c r="E38" s="4">
+        <v>1</v>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2642,7 +2759,10 @@
       <c r="D39" s="4">
         <v>1</v>
       </c>
-      <c r="E39" s="6" t="inlineStr">
+      <c r="E39" s="4">
+        <v>1</v>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -2668,9 +2788,12 @@
         </is>
       </c>
       <c r="D40" s="4">
+        <v>5</v>
+      </c>
+      <c r="E40" s="4">
         <v>1</v>
       </c>
-      <c r="E40" s="6" t="inlineStr">
+      <c r="F40" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2724,9 +2847,12 @@
         </is>
       </c>
       <c r="D41" s="4">
+        <v>5</v>
+      </c>
+      <c r="E41" s="4">
         <v>2</v>
       </c>
-      <c r="E41" s="6" t="inlineStr">
+      <c r="F41" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2780,9 +2906,12 @@
         </is>
       </c>
       <c r="D42" s="4">
+        <v>5</v>
+      </c>
+      <c r="E42" s="4">
         <v>3</v>
       </c>
-      <c r="E42" s="6" t="inlineStr">
+      <c r="F42" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2838,7 +2967,10 @@
       <c r="D43" s="4">
         <v>1</v>
       </c>
-      <c r="E43" s="6" t="inlineStr">
+      <c r="E43" s="4">
+        <v>1</v>
+      </c>
+      <c r="F43" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -2864,9 +2996,12 @@
         </is>
       </c>
       <c r="D44" s="4">
+        <v>12</v>
+      </c>
+      <c r="E44" s="4">
         <v>1</v>
       </c>
-      <c r="E44" s="6" t="inlineStr">
+      <c r="F44" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2920,9 +3055,12 @@
         </is>
       </c>
       <c r="D45" s="4">
+        <v>12</v>
+      </c>
+      <c r="E45" s="4">
         <v>2</v>
       </c>
-      <c r="E45" s="6" t="inlineStr">
+      <c r="F45" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2976,9 +3114,12 @@
         </is>
       </c>
       <c r="D46" s="4">
+        <v>12</v>
+      </c>
+      <c r="E46" s="4">
         <v>3</v>
       </c>
-      <c r="E46" s="6" t="inlineStr">
+      <c r="F46" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3032,9 +3173,12 @@
         </is>
       </c>
       <c r="D47" s="4">
+        <v>12</v>
+      </c>
+      <c r="E47" s="4">
         <v>4</v>
       </c>
-      <c r="E47" s="6" t="inlineStr">
+      <c r="F47" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3088,9 +3232,12 @@
         </is>
       </c>
       <c r="D48" s="4">
+        <v>12</v>
+      </c>
+      <c r="E48" s="4">
         <v>5</v>
       </c>
-      <c r="E48" s="6" t="inlineStr">
+      <c r="F48" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3144,9 +3291,12 @@
         </is>
       </c>
       <c r="D49" s="4">
+        <v>4</v>
+      </c>
+      <c r="E49" s="4">
         <v>1</v>
       </c>
-      <c r="E49" s="6" t="inlineStr">
+      <c r="F49" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3207,9 +3357,12 @@
         </is>
       </c>
       <c r="D50" s="4">
+        <v>4</v>
+      </c>
+      <c r="E50" s="4">
         <v>2</v>
       </c>
-      <c r="E50" s="6" t="inlineStr">
+      <c r="F50" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3270,9 +3423,12 @@
         </is>
       </c>
       <c r="D51" s="4">
+        <v>4</v>
+      </c>
+      <c r="E51" s="4">
         <v>3</v>
       </c>
-      <c r="E51" s="6" t="inlineStr">
+      <c r="F51" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3333,9 +3489,12 @@
         </is>
       </c>
       <c r="D52" s="4">
+        <v>7</v>
+      </c>
+      <c r="E52" s="4">
         <v>1</v>
       </c>
-      <c r="E52" s="6" t="inlineStr">
+      <c r="F52" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3396,9 +3555,12 @@
         </is>
       </c>
       <c r="D53" s="4">
+        <v>7</v>
+      </c>
+      <c r="E53" s="4">
         <v>2</v>
       </c>
-      <c r="E53" s="6" t="inlineStr">
+      <c r="F53" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3459,9 +3621,12 @@
         </is>
       </c>
       <c r="D54" s="4">
+        <v>7</v>
+      </c>
+      <c r="E54" s="4">
         <v>3</v>
       </c>
-      <c r="E54" s="6" t="inlineStr">
+      <c r="F54" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3522,9 +3687,12 @@
         </is>
       </c>
       <c r="D55" s="4">
+        <v>7</v>
+      </c>
+      <c r="E55" s="4">
         <v>4</v>
       </c>
-      <c r="E55" s="6" t="inlineStr">
+      <c r="F55" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3585,9 +3753,12 @@
         </is>
       </c>
       <c r="D56" s="4">
+        <v>6</v>
+      </c>
+      <c r="E56" s="4">
         <v>1</v>
       </c>
-      <c r="E56" s="6" t="inlineStr">
+      <c r="F56" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3656,9 +3827,12 @@
         </is>
       </c>
       <c r="D57" s="4">
+        <v>6</v>
+      </c>
+      <c r="E57" s="4">
         <v>2</v>
       </c>
-      <c r="E57" s="6" t="inlineStr">
+      <c r="F57" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3727,9 +3901,12 @@
         </is>
       </c>
       <c r="D58" s="4">
+        <v>6</v>
+      </c>
+      <c r="E58" s="4">
         <v>3</v>
       </c>
-      <c r="E58" s="6" t="inlineStr">
+      <c r="F58" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3800,7 +3977,10 @@
       <c r="D59" s="4">
         <v>1</v>
       </c>
-      <c r="E59" s="6" t="inlineStr">
+      <c r="E59" s="4">
+        <v>1</v>
+      </c>
+      <c r="F59" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -3826,9 +4006,12 @@
         </is>
       </c>
       <c r="D60" s="4">
+        <v>3</v>
+      </c>
+      <c r="E60" s="4">
         <v>1</v>
       </c>
-      <c r="E60" s="6" t="inlineStr">
+      <c r="F60" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3897,9 +4080,12 @@
         </is>
       </c>
       <c r="D61" s="4">
+        <v>3</v>
+      </c>
+      <c r="E61" s="4">
         <v>2</v>
       </c>
-      <c r="E61" s="6" t="inlineStr">
+      <c r="F61" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3970,7 +4156,10 @@
       <c r="D62" s="4">
         <v>1</v>
       </c>
-      <c r="E62" s="6" t="inlineStr">
+      <c r="E62" s="4">
+        <v>1</v>
+      </c>
+      <c r="F62" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -3998,7 +4187,10 @@
       <c r="D63" s="4">
         <v>1</v>
       </c>
-      <c r="E63" s="6" t="inlineStr">
+      <c r="E63" s="4">
+        <v>1</v>
+      </c>
+      <c r="F63" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4076,7 +4268,10 @@
       <c r="D64" s="4">
         <v>1</v>
       </c>
-      <c r="E64" s="6" t="inlineStr">
+      <c r="E64" s="4">
+        <v>1</v>
+      </c>
+      <c r="F64" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -4104,7 +4299,10 @@
       <c r="D65" s="4">
         <v>1</v>
       </c>
-      <c r="E65" s="6" t="inlineStr">
+      <c r="E65" s="4">
+        <v>1</v>
+      </c>
+      <c r="F65" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -4132,7 +4330,10 @@
       <c r="D66" s="4">
         <v>1</v>
       </c>
-      <c r="E66" s="6" t="inlineStr">
+      <c r="E66" s="4">
+        <v>1</v>
+      </c>
+      <c r="F66" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4223,9 +4424,12 @@
         </is>
       </c>
       <c r="D67" s="4">
+        <v>8</v>
+      </c>
+      <c r="E67" s="4">
         <v>1</v>
       </c>
-      <c r="E67" s="6" t="inlineStr">
+      <c r="F67" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4279,9 +4483,12 @@
         </is>
       </c>
       <c r="D68" s="4">
+        <v>8</v>
+      </c>
+      <c r="E68" s="4">
         <v>2</v>
       </c>
-      <c r="E68" s="6" t="inlineStr">
+      <c r="F68" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4335,9 +4542,12 @@
         </is>
       </c>
       <c r="D69" s="4">
+        <v>8</v>
+      </c>
+      <c r="E69" s="4">
         <v>3</v>
       </c>
-      <c r="E69" s="6" t="inlineStr">
+      <c r="F69" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4391,9 +4601,12 @@
         </is>
       </c>
       <c r="D70" s="4">
+        <v>8</v>
+      </c>
+      <c r="E70" s="4">
         <v>4</v>
       </c>
-      <c r="E70" s="6" t="inlineStr">
+      <c r="F70" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4447,9 +4660,12 @@
         </is>
       </c>
       <c r="D71" s="4">
+        <v>5</v>
+      </c>
+      <c r="E71" s="4">
         <v>1</v>
       </c>
-      <c r="E71" s="6" t="inlineStr">
+      <c r="F71" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4503,9 +4719,12 @@
         </is>
       </c>
       <c r="D72" s="4">
+        <v>5</v>
+      </c>
+      <c r="E72" s="4">
         <v>2</v>
       </c>
-      <c r="E72" s="6" t="inlineStr">
+      <c r="F72" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4559,9 +4778,12 @@
         </is>
       </c>
       <c r="D73" s="4">
+        <v>5</v>
+      </c>
+      <c r="E73" s="4">
         <v>3</v>
       </c>
-      <c r="E73" s="6" t="inlineStr">
+      <c r="F73" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4615,9 +4837,12 @@
         </is>
       </c>
       <c r="D74" s="4">
+        <v>5</v>
+      </c>
+      <c r="E74" s="4">
         <v>4</v>
       </c>
-      <c r="E74" s="6" t="inlineStr">
+      <c r="F74" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4673,7 +4898,10 @@
       <c r="D75" s="4">
         <v>5</v>
       </c>
-      <c r="E75" s="6" t="inlineStr">
+      <c r="E75" s="4">
+        <v>5</v>
+      </c>
+      <c r="F75" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4727,9 +4955,12 @@
         </is>
       </c>
       <c r="D76" s="4">
+        <v>2</v>
+      </c>
+      <c r="E76" s="4">
         <v>1</v>
       </c>
-      <c r="E76" s="6" t="inlineStr">
+      <c r="F76" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -4755,9 +4986,12 @@
         </is>
       </c>
       <c r="D77" s="4">
+        <v>2</v>
+      </c>
+      <c r="E77" s="4">
         <v>1</v>
       </c>
-      <c r="E77" s="6" t="inlineStr">
+      <c r="F77" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -4785,7 +5019,10 @@
       <c r="D78" s="4">
         <v>1</v>
       </c>
-      <c r="E78" s="6" t="inlineStr">
+      <c r="E78" s="4">
+        <v>1</v>
+      </c>
+      <c r="F78" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -4811,9 +5048,12 @@
         </is>
       </c>
       <c r="D79" s="4">
+        <v>2</v>
+      </c>
+      <c r="E79" s="4">
         <v>1</v>
       </c>
-      <c r="E79" s="6" t="inlineStr">
+      <c r="F79" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4874,9 +5114,12 @@
         </is>
       </c>
       <c r="D80" s="4">
+        <v>2</v>
+      </c>
+      <c r="E80" s="4">
         <v>1</v>
       </c>
-      <c r="E80" s="6" t="inlineStr">
+      <c r="F80" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4947,7 +5190,10 @@
       <c r="D81" s="4">
         <v>2</v>
       </c>
-      <c r="E81" s="6" t="inlineStr">
+      <c r="E81" s="4">
+        <v>2</v>
+      </c>
+      <c r="F81" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5018,7 +5264,10 @@
       <c r="D82" s="4">
         <v>1</v>
       </c>
-      <c r="E82" s="6" t="inlineStr">
+      <c r="E82" s="4">
+        <v>1</v>
+      </c>
+      <c r="F82" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5087,9 +5336,12 @@
         </is>
       </c>
       <c r="D83" s="4">
+        <v>3</v>
+      </c>
+      <c r="E83" s="4">
         <v>1</v>
       </c>
-      <c r="E83" s="6" t="inlineStr">
+      <c r="F83" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5158,9 +5410,12 @@
         </is>
       </c>
       <c r="D84" s="4">
+        <v>6</v>
+      </c>
+      <c r="E84" s="4">
         <v>1</v>
       </c>
-      <c r="E84" s="6" t="inlineStr">
+      <c r="F84" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5236,9 +5491,12 @@
         </is>
       </c>
       <c r="D85" s="4">
+        <v>6</v>
+      </c>
+      <c r="E85" s="4">
         <v>2</v>
       </c>
-      <c r="E85" s="6" t="inlineStr">
+      <c r="F85" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5314,9 +5572,12 @@
         </is>
       </c>
       <c r="D86" s="4">
+        <v>6</v>
+      </c>
+      <c r="E86" s="4">
         <v>3</v>
       </c>
-      <c r="E86" s="6" t="inlineStr">
+      <c r="F86" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5392,9 +5653,12 @@
         </is>
       </c>
       <c r="D87" s="4">
+        <v>2</v>
+      </c>
+      <c r="E87" s="4">
         <v>1</v>
       </c>
-      <c r="E87" s="6" t="inlineStr">
+      <c r="F87" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5472,7 +5736,10 @@
       <c r="D88" s="4">
         <v>2</v>
       </c>
-      <c r="E88" s="6" t="inlineStr">
+      <c r="E88" s="4">
+        <v>2</v>
+      </c>
+      <c r="F88" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5548,9 +5815,12 @@
         </is>
       </c>
       <c r="D89" s="4">
+        <v>2</v>
+      </c>
+      <c r="E89" s="4">
         <v>1</v>
       </c>
-      <c r="E89" s="6" t="inlineStr">
+      <c r="F89" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5628,7 +5898,10 @@
       <c r="D90" s="4">
         <v>2</v>
       </c>
-      <c r="E90" s="6" t="inlineStr">
+      <c r="E90" s="4">
+        <v>2</v>
+      </c>
+      <c r="F90" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5704,9 +5977,12 @@
         </is>
       </c>
       <c r="D91" s="4">
+        <v>4</v>
+      </c>
+      <c r="E91" s="4">
         <v>1</v>
       </c>
-      <c r="E91" s="6" t="inlineStr">
+      <c r="F91" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5790,9 +6066,12 @@
         </is>
       </c>
       <c r="D92" s="4">
+        <v>4</v>
+      </c>
+      <c r="E92" s="4">
         <v>2</v>
       </c>
-      <c r="E92" s="6" t="inlineStr">
+      <c r="F92" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5876,9 +6155,12 @@
         </is>
       </c>
       <c r="D93" s="4">
+        <v>4</v>
+      </c>
+      <c r="E93" s="4">
         <v>3</v>
       </c>
-      <c r="E93" s="6" t="inlineStr">
+      <c r="F93" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5962,9 +6244,12 @@
         </is>
       </c>
       <c r="D94" s="4">
+        <v>3</v>
+      </c>
+      <c r="E94" s="4">
         <v>1</v>
       </c>
-      <c r="E94" s="6" t="inlineStr">
+      <c r="F94" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -5990,9 +6275,12 @@
         </is>
       </c>
       <c r="D95" s="4">
+        <v>4</v>
+      </c>
+      <c r="E95" s="4">
         <v>1</v>
       </c>
-      <c r="E95" s="6" t="inlineStr">
+      <c r="F95" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6076,9 +6364,12 @@
         </is>
       </c>
       <c r="D96" s="4">
+        <v>4</v>
+      </c>
+      <c r="E96" s="4">
         <v>2</v>
       </c>
-      <c r="E96" s="6" t="inlineStr">
+      <c r="F96" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6162,9 +6453,12 @@
         </is>
       </c>
       <c r="D97" s="4">
+        <v>4</v>
+      </c>
+      <c r="E97" s="4">
         <v>1</v>
       </c>
-      <c r="E97" s="6" t="inlineStr">
+      <c r="F97" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6255,9 +6549,12 @@
         </is>
       </c>
       <c r="D98" s="4">
+        <v>4</v>
+      </c>
+      <c r="E98" s="4">
         <v>2</v>
       </c>
-      <c r="E98" s="6" t="inlineStr">
+      <c r="F98" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6348,9 +6645,12 @@
         </is>
       </c>
       <c r="D99" s="4">
+        <v>2</v>
+      </c>
+      <c r="E99" s="4">
         <v>1</v>
       </c>
-      <c r="E99" s="6" t="inlineStr">
+      <c r="F99" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6441,9 +6741,12 @@
         </is>
       </c>
       <c r="D100" s="4">
+        <v>2</v>
+      </c>
+      <c r="E100" s="4">
         <v>1</v>
       </c>
-      <c r="E100" s="6" t="inlineStr">
+      <c r="F100" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6534,9 +6837,12 @@
         </is>
       </c>
       <c r="D101" s="4">
+        <v>3</v>
+      </c>
+      <c r="E101" s="4">
         <v>1</v>
       </c>
-      <c r="E101" s="6" t="inlineStr">
+      <c r="F101" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -6562,9 +6868,12 @@
         </is>
       </c>
       <c r="D102" s="4">
+        <v>3</v>
+      </c>
+      <c r="E102" s="4">
         <v>1</v>
       </c>
-      <c r="E102" s="6" t="inlineStr">
+      <c r="F102" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6663,9 +6972,12 @@
         </is>
       </c>
       <c r="D103" s="4">
+        <v>3</v>
+      </c>
+      <c r="E103" s="4">
         <v>2</v>
       </c>
-      <c r="E103" s="6" t="inlineStr">
+      <c r="F103" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6766,7 +7078,10 @@
       <c r="D104" s="4">
         <v>3</v>
       </c>
-      <c r="E104" s="6" t="inlineStr">
+      <c r="E104" s="4">
+        <v>3</v>
+      </c>
+      <c r="F104" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6867,7 +7182,10 @@
       <c r="D105" s="4">
         <v>1</v>
       </c>
-      <c r="E105" s="6" t="inlineStr">
+      <c r="E105" s="4">
+        <v>1</v>
+      </c>
+      <c r="F105" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6973,9 +7291,12 @@
         </is>
       </c>
       <c r="D106" s="4">
+        <v>3</v>
+      </c>
+      <c r="E106" s="4">
         <v>1</v>
       </c>
-      <c r="E106" s="6" t="inlineStr">
+      <c r="F106" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7081,9 +7402,12 @@
         </is>
       </c>
       <c r="D107" s="4">
+        <v>3</v>
+      </c>
+      <c r="E107" s="4">
         <v>2</v>
       </c>
-      <c r="E107" s="6" t="inlineStr">
+      <c r="F107" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7191,7 +7515,10 @@
       <c r="D108" s="4">
         <v>1</v>
       </c>
-      <c r="E108" s="6" t="inlineStr">
+      <c r="E108" s="4">
+        <v>1</v>
+      </c>
+      <c r="F108" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -7217,9 +7544,12 @@
         </is>
       </c>
       <c r="D109" s="4">
+        <v>2</v>
+      </c>
+      <c r="E109" s="4">
         <v>1</v>
       </c>
-      <c r="E109" s="6" t="inlineStr">
+      <c r="F109" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -7245,9 +7575,12 @@
         </is>
       </c>
       <c r="D110" s="4">
+        <v>3</v>
+      </c>
+      <c r="E110" s="4">
         <v>1</v>
       </c>
-      <c r="E110" s="6" t="inlineStr">
+      <c r="F110" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7361,9 +7694,12 @@
         </is>
       </c>
       <c r="D111" s="4">
+        <v>3</v>
+      </c>
+      <c r="E111" s="4">
         <v>2</v>
       </c>
-      <c r="E111" s="6" t="inlineStr">
+      <c r="F111" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7479,7 +7815,10 @@
       <c r="D112" s="4">
         <v>3</v>
       </c>
-      <c r="E112" s="6" t="inlineStr">
+      <c r="E112" s="4">
+        <v>3</v>
+      </c>
+      <c r="F112" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7593,9 +7932,12 @@
         </is>
       </c>
       <c r="D113" s="4">
+        <v>7</v>
+      </c>
+      <c r="E113" s="4">
         <v>1</v>
       </c>
-      <c r="E113" s="6" t="inlineStr">
+      <c r="F113" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7649,9 +7991,12 @@
         </is>
       </c>
       <c r="D114" s="4">
+        <v>7</v>
+      </c>
+      <c r="E114" s="4">
         <v>2</v>
       </c>
-      <c r="E114" s="6" t="inlineStr">
+      <c r="F114" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7705,9 +8050,12 @@
         </is>
       </c>
       <c r="D115" s="4">
+        <v>8</v>
+      </c>
+      <c r="E115" s="4">
         <v>1</v>
       </c>
-      <c r="E115" s="6" t="inlineStr">
+      <c r="F115" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7761,9 +8109,12 @@
         </is>
       </c>
       <c r="D116" s="4">
+        <v>8</v>
+      </c>
+      <c r="E116" s="4">
         <v>2</v>
       </c>
-      <c r="E116" s="6" t="inlineStr">
+      <c r="F116" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7817,9 +8168,12 @@
         </is>
       </c>
       <c r="D117" s="4">
+        <v>8</v>
+      </c>
+      <c r="E117" s="4">
         <v>3</v>
       </c>
-      <c r="E117" s="6" t="inlineStr">
+      <c r="F117" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7873,9 +8227,12 @@
         </is>
       </c>
       <c r="D118" s="4">
+        <v>8</v>
+      </c>
+      <c r="E118" s="4">
         <v>4</v>
       </c>
-      <c r="E118" s="6" t="inlineStr">
+      <c r="F118" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7929,9 +8286,12 @@
         </is>
       </c>
       <c r="D119" s="4">
+        <v>8</v>
+      </c>
+      <c r="E119" s="4">
         <v>5</v>
       </c>
-      <c r="E119" s="6" t="inlineStr">
+      <c r="F119" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7985,9 +8345,12 @@
         </is>
       </c>
       <c r="D120" s="4">
+        <v>3</v>
+      </c>
+      <c r="E120" s="4">
         <v>1</v>
       </c>
-      <c r="E120" s="6" t="inlineStr">
+      <c r="F120" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8041,9 +8404,12 @@
         </is>
       </c>
       <c r="D121" s="4">
+        <v>3</v>
+      </c>
+      <c r="E121" s="4">
         <v>2</v>
       </c>
-      <c r="E121" s="6" t="inlineStr">
+      <c r="F121" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8099,7 +8465,10 @@
       <c r="D122" s="4">
         <v>3</v>
       </c>
-      <c r="E122" s="6" t="inlineStr">
+      <c r="E122" s="4">
+        <v>3</v>
+      </c>
+      <c r="F122" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8155,7 +8524,10 @@
       <c r="D123" s="4">
         <v>1</v>
       </c>
-      <c r="E123" s="6" t="inlineStr">
+      <c r="E123" s="4">
+        <v>1</v>
+      </c>
+      <c r="F123" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8218,7 +8590,10 @@
       <c r="D124" s="4">
         <v>1</v>
       </c>
-      <c r="E124" s="6" t="inlineStr">
+      <c r="E124" s="4">
+        <v>1</v>
+      </c>
+      <c r="F124" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8287,9 +8662,12 @@
         </is>
       </c>
       <c r="D125" s="4">
+        <v>2</v>
+      </c>
+      <c r="E125" s="4">
         <v>1</v>
       </c>
-      <c r="E125" s="6" t="inlineStr">
+      <c r="F125" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -8315,9 +8693,12 @@
         </is>
       </c>
       <c r="D126" s="4">
+        <v>6</v>
+      </c>
+      <c r="E126" s="4">
         <v>1</v>
       </c>
-      <c r="E126" s="6" t="inlineStr">
+      <c r="F126" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8386,9 +8767,12 @@
         </is>
       </c>
       <c r="D127" s="4">
+        <v>6</v>
+      </c>
+      <c r="E127" s="4">
         <v>2</v>
       </c>
-      <c r="E127" s="6" t="inlineStr">
+      <c r="F127" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8457,9 +8841,12 @@
         </is>
       </c>
       <c r="D128" s="4">
+        <v>6</v>
+      </c>
+      <c r="E128" s="4">
         <v>3</v>
       </c>
-      <c r="E128" s="6" t="inlineStr">
+      <c r="F128" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8528,9 +8915,12 @@
         </is>
       </c>
       <c r="D129" s="4">
+        <v>6</v>
+      </c>
+      <c r="E129" s="4">
         <v>4</v>
       </c>
-      <c r="E129" s="6" t="inlineStr">
+      <c r="F129" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8599,9 +8989,12 @@
         </is>
       </c>
       <c r="D130" s="4">
+        <v>5</v>
+      </c>
+      <c r="E130" s="4">
         <v>1</v>
       </c>
-      <c r="E130" s="6" t="inlineStr">
+      <c r="F130" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8677,9 +9070,12 @@
         </is>
       </c>
       <c r="D131" s="4">
+        <v>5</v>
+      </c>
+      <c r="E131" s="4">
         <v>2</v>
       </c>
-      <c r="E131" s="6" t="inlineStr">
+      <c r="F131" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8755,9 +9151,12 @@
         </is>
       </c>
       <c r="D132" s="4">
+        <v>3</v>
+      </c>
+      <c r="E132" s="4">
         <v>1</v>
       </c>
-      <c r="E132" s="6" t="inlineStr">
+      <c r="F132" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8833,9 +9232,12 @@
         </is>
       </c>
       <c r="D133" s="4">
+        <v>3</v>
+      </c>
+      <c r="E133" s="4">
         <v>2</v>
       </c>
-      <c r="E133" s="6" t="inlineStr">
+      <c r="F133" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8911,9 +9313,12 @@
         </is>
       </c>
       <c r="D134" s="4">
+        <v>4</v>
+      </c>
+      <c r="E134" s="4">
         <v>1</v>
       </c>
-      <c r="E134" s="6" t="inlineStr">
+      <c r="F134" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8989,9 +9394,12 @@
         </is>
       </c>
       <c r="D135" s="4">
+        <v>4</v>
+      </c>
+      <c r="E135" s="4">
         <v>2</v>
       </c>
-      <c r="E135" s="6" t="inlineStr">
+      <c r="F135" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9067,9 +9475,12 @@
         </is>
       </c>
       <c r="D136" s="4">
+        <v>2</v>
+      </c>
+      <c r="E136" s="4">
         <v>1</v>
       </c>
-      <c r="E136" s="6" t="inlineStr">
+      <c r="F136" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9155,7 +9566,10 @@
       <c r="D137" s="4">
         <v>2</v>
       </c>
-      <c r="E137" s="6" t="inlineStr">
+      <c r="E137" s="4">
+        <v>2</v>
+      </c>
+      <c r="F137" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9241,7 +9655,10 @@
       <c r="D138" s="4">
         <v>1</v>
       </c>
-      <c r="E138" s="6" t="inlineStr">
+      <c r="E138" s="4">
+        <v>1</v>
+      </c>
+      <c r="F138" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9325,9 +9742,12 @@
         </is>
       </c>
       <c r="D139" s="4">
+        <v>2</v>
+      </c>
+      <c r="E139" s="4">
         <v>1</v>
       </c>
-      <c r="E139" s="6" t="inlineStr">
+      <c r="F139" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9411,9 +9831,12 @@
         </is>
       </c>
       <c r="D140" s="4">
+        <v>3</v>
+      </c>
+      <c r="E140" s="4">
         <v>1</v>
       </c>
-      <c r="E140" s="6" t="inlineStr">
+      <c r="F140" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -9439,9 +9862,12 @@
         </is>
       </c>
       <c r="D141" s="4">
+        <v>2</v>
+      </c>
+      <c r="E141" s="4">
         <v>1</v>
       </c>
-      <c r="E141" s="6" t="inlineStr">
+      <c r="F141" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9532,9 +9958,12 @@
         </is>
       </c>
       <c r="D142" s="4">
+        <v>2</v>
+      </c>
+      <c r="E142" s="4">
         <v>1</v>
       </c>
-      <c r="E142" s="6" t="inlineStr">
+      <c r="F142" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9633,9 +10062,12 @@
         </is>
       </c>
       <c r="D143" s="4">
+        <v>2</v>
+      </c>
+      <c r="E143" s="4">
         <v>1</v>
       </c>
-      <c r="E143" s="6" t="inlineStr">
+      <c r="F143" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -9661,9 +10093,12 @@
         </is>
       </c>
       <c r="D144" s="4">
+        <v>2</v>
+      </c>
+      <c r="E144" s="4">
         <v>1</v>
       </c>
-      <c r="E144" s="6" t="inlineStr">
+      <c r="F144" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -9691,7 +10126,10 @@
       <c r="D145" s="4">
         <v>1</v>
       </c>
-      <c r="E145" s="6" t="inlineStr">
+      <c r="E145" s="4">
+        <v>1</v>
+      </c>
+      <c r="F145" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -9719,7 +10157,10 @@
       <c r="D146" s="4">
         <v>1</v>
       </c>
-      <c r="E146" s="6" t="inlineStr">
+      <c r="E146" s="4">
+        <v>1</v>
+      </c>
+      <c r="F146" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -9745,9 +10186,12 @@
         </is>
       </c>
       <c r="D147" s="4">
+        <v>2</v>
+      </c>
+      <c r="E147" s="4">
         <v>1</v>
       </c>
-      <c r="E147" s="6" t="inlineStr">
+      <c r="F147" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9801,9 +10245,12 @@
         </is>
       </c>
       <c r="D148" s="4">
+        <v>4</v>
+      </c>
+      <c r="E148" s="4">
         <v>1</v>
       </c>
-      <c r="E148" s="6" t="inlineStr">
+      <c r="F148" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9857,9 +10304,12 @@
         </is>
       </c>
       <c r="D149" s="4">
+        <v>4</v>
+      </c>
+      <c r="E149" s="4">
         <v>2</v>
       </c>
-      <c r="E149" s="6" t="inlineStr">
+      <c r="F149" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9913,9 +10363,12 @@
         </is>
       </c>
       <c r="D150" s="4">
+        <v>4</v>
+      </c>
+      <c r="E150" s="4">
         <v>3</v>
       </c>
-      <c r="E150" s="6" t="inlineStr">
+      <c r="F150" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9969,9 +10422,12 @@
         </is>
       </c>
       <c r="D151" s="4">
+        <v>2</v>
+      </c>
+      <c r="E151" s="4">
         <v>1</v>
       </c>
-      <c r="E151" s="6" t="inlineStr">
+      <c r="F151" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -9999,7 +10455,10 @@
       <c r="D152" s="4">
         <v>1</v>
       </c>
-      <c r="E152" s="6" t="inlineStr">
+      <c r="E152" s="4">
+        <v>1</v>
+      </c>
+      <c r="F152" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -10025,9 +10484,12 @@
         </is>
       </c>
       <c r="D153" s="4">
+        <v>3</v>
+      </c>
+      <c r="E153" s="4">
         <v>1</v>
       </c>
-      <c r="E153" s="6" t="inlineStr">
+      <c r="F153" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10096,9 +10558,12 @@
         </is>
       </c>
       <c r="D154" s="4">
+        <v>2</v>
+      </c>
+      <c r="E154" s="4">
         <v>1</v>
       </c>
-      <c r="E154" s="6" t="inlineStr">
+      <c r="F154" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -10126,7 +10591,10 @@
       <c r="D155" s="4">
         <v>1</v>
       </c>
-      <c r="E155" s="6" t="inlineStr">
+      <c r="E155" s="4">
+        <v>1</v>
+      </c>
+      <c r="F155" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10195,9 +10663,12 @@
         </is>
       </c>
       <c r="D156" s="4">
+        <v>17</v>
+      </c>
+      <c r="E156" s="4">
         <v>1</v>
       </c>
-      <c r="E156" s="6" t="inlineStr">
+      <c r="F156" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10273,9 +10744,12 @@
         </is>
       </c>
       <c r="D157" s="4">
+        <v>17</v>
+      </c>
+      <c r="E157" s="4">
         <v>2</v>
       </c>
-      <c r="E157" s="6" t="inlineStr">
+      <c r="F157" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10351,9 +10825,12 @@
         </is>
       </c>
       <c r="D158" s="4">
+        <v>2</v>
+      </c>
+      <c r="E158" s="4">
         <v>1</v>
       </c>
-      <c r="E158" s="6" t="inlineStr">
+      <c r="F158" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10431,7 +10908,10 @@
       <c r="D159" s="4">
         <v>1</v>
       </c>
-      <c r="E159" s="6" t="inlineStr">
+      <c r="E159" s="4">
+        <v>1</v>
+      </c>
+      <c r="F159" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10517,7 +10997,10 @@
       <c r="D160" s="4">
         <v>1</v>
       </c>
-      <c r="E160" s="6" t="inlineStr">
+      <c r="E160" s="4">
+        <v>1</v>
+      </c>
+      <c r="F160" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10601,9 +11084,12 @@
         </is>
       </c>
       <c r="D161" s="4">
+        <v>4</v>
+      </c>
+      <c r="E161" s="4">
         <v>1</v>
       </c>
-      <c r="E161" s="6" t="inlineStr">
+      <c r="F161" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10687,9 +11173,12 @@
         </is>
       </c>
       <c r="D162" s="4">
+        <v>4</v>
+      </c>
+      <c r="E162" s="4">
         <v>2</v>
       </c>
-      <c r="E162" s="6" t="inlineStr">
+      <c r="F162" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10773,9 +11262,12 @@
         </is>
       </c>
       <c r="D163" s="4">
+        <v>3</v>
+      </c>
+      <c r="E163" s="4">
         <v>1</v>
       </c>
-      <c r="E163" s="6" t="inlineStr">
+      <c r="F163" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10866,9 +11358,12 @@
         </is>
       </c>
       <c r="D164" s="4">
+        <v>3</v>
+      </c>
+      <c r="E164" s="4">
         <v>1</v>
       </c>
-      <c r="E164" s="6" t="inlineStr">
+      <c r="F164" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10959,9 +11454,12 @@
         </is>
       </c>
       <c r="D165" s="4">
+        <v>2</v>
+      </c>
+      <c r="E165" s="4">
         <v>1</v>
       </c>
-      <c r="E165" s="6" t="inlineStr">
+      <c r="F165" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11060,9 +11558,12 @@
         </is>
       </c>
       <c r="D166" s="4">
+        <v>2</v>
+      </c>
+      <c r="E166" s="4">
         <v>1</v>
       </c>
-      <c r="E166" s="6" t="inlineStr">
+      <c r="F166" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11168,9 +11669,12 @@
         </is>
       </c>
       <c r="D167" s="4">
+        <v>2</v>
+      </c>
+      <c r="E167" s="4">
         <v>1</v>
       </c>
-      <c r="E167" s="6" t="inlineStr">
+      <c r="F167" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11278,7 +11782,10 @@
       <c r="D168" s="4">
         <v>2</v>
       </c>
-      <c r="E168" s="6" t="inlineStr">
+      <c r="E168" s="4">
+        <v>2</v>
+      </c>
+      <c r="F168" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11384,9 +11891,12 @@
         </is>
       </c>
       <c r="D169" s="4">
+        <v>3</v>
+      </c>
+      <c r="E169" s="4">
         <v>1</v>
       </c>
-      <c r="E169" s="6" t="inlineStr">
+      <c r="F169" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -11414,7 +11924,10 @@
       <c r="D170" s="4">
         <v>1</v>
       </c>
-      <c r="E170" s="6" t="inlineStr">
+      <c r="E170" s="4">
+        <v>1</v>
+      </c>
+      <c r="F170" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -11442,7 +11955,10 @@
       <c r="D171" s="4">
         <v>1</v>
       </c>
-      <c r="E171" s="6" t="inlineStr">
+      <c r="E171" s="4">
+        <v>1</v>
+      </c>
+      <c r="F171" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -11470,7 +11986,10 @@
       <c r="D172" s="4">
         <v>1</v>
       </c>
-      <c r="E172" s="6" t="inlineStr">
+      <c r="E172" s="4">
+        <v>1</v>
+      </c>
+      <c r="F172" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -11496,9 +12015,12 @@
         </is>
       </c>
       <c r="D173" s="4">
+        <v>4</v>
+      </c>
+      <c r="E173" s="4">
         <v>1</v>
       </c>
-      <c r="E173" s="6" t="inlineStr">
+      <c r="F173" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11552,9 +12074,12 @@
         </is>
       </c>
       <c r="D174" s="4">
+        <v>4</v>
+      </c>
+      <c r="E174" s="4">
         <v>2</v>
       </c>
-      <c r="E174" s="6" t="inlineStr">
+      <c r="F174" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11608,9 +12133,12 @@
         </is>
       </c>
       <c r="D175" s="4">
+        <v>4</v>
+      </c>
+      <c r="E175" s="4">
         <v>3</v>
       </c>
-      <c r="E175" s="6" t="inlineStr">
+      <c r="F175" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11666,7 +12194,10 @@
       <c r="D176" s="4">
         <v>1</v>
       </c>
-      <c r="E176" s="6" t="inlineStr">
+      <c r="E176" s="4">
+        <v>1</v>
+      </c>
+      <c r="F176" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11722,7 +12253,10 @@
       <c r="D177" s="4">
         <v>1</v>
       </c>
-      <c r="E177" s="6" t="inlineStr">
+      <c r="E177" s="4">
+        <v>1</v>
+      </c>
+      <c r="F177" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11800,7 +12334,10 @@
       <c r="D178" s="4">
         <v>1</v>
       </c>
-      <c r="E178" s="6" t="inlineStr">
+      <c r="E178" s="4">
+        <v>1</v>
+      </c>
+      <c r="F178" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11899,9 +12436,12 @@
         </is>
       </c>
       <c r="D179" s="4">
+        <v>2</v>
+      </c>
+      <c r="E179" s="4">
         <v>1</v>
       </c>
-      <c r="E179" s="6" t="inlineStr">
+      <c r="F179" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11957,7 +12497,10 @@
       <c r="D180" s="4">
         <v>2</v>
       </c>
-      <c r="E180" s="6" t="inlineStr">
+      <c r="E180" s="4">
+        <v>2</v>
+      </c>
+      <c r="F180" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12013,7 +12556,10 @@
       <c r="D181" s="4">
         <v>1</v>
       </c>
-      <c r="E181" s="6" t="inlineStr">
+      <c r="E181" s="4">
+        <v>1</v>
+      </c>
+      <c r="F181" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12069,7 +12615,10 @@
       <c r="D182" s="4">
         <v>1</v>
       </c>
-      <c r="E182" s="6" t="inlineStr">
+      <c r="E182" s="4">
+        <v>1</v>
+      </c>
+      <c r="F182" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -12097,7 +12646,10 @@
       <c r="D183" s="4">
         <v>1</v>
       </c>
-      <c r="E183" s="6" t="inlineStr">
+      <c r="E183" s="4">
+        <v>1</v>
+      </c>
+      <c r="F183" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12175,7 +12727,10 @@
       <c r="D184" s="4">
         <v>1</v>
       </c>
-      <c r="E184" s="6" t="inlineStr">
+      <c r="E184" s="4">
+        <v>1</v>
+      </c>
+      <c r="F184" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12283,7 +12838,10 @@
       <c r="D185" s="4">
         <v>1</v>
       </c>
-      <c r="E185" s="6" t="inlineStr">
+      <c r="E185" s="4">
+        <v>1</v>
+      </c>
+      <c r="F185" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12391,7 +12949,10 @@
       <c r="D186" s="4">
         <v>1</v>
       </c>
-      <c r="E186" s="6" t="inlineStr">
+      <c r="E186" s="4">
+        <v>1</v>
+      </c>
+      <c r="F186" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -12417,9 +12978,12 @@
         </is>
       </c>
       <c r="D187" s="4">
+        <v>4</v>
+      </c>
+      <c r="E187" s="4">
         <v>1</v>
       </c>
-      <c r="E187" s="6" t="inlineStr">
+      <c r="F187" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12473,9 +13037,12 @@
         </is>
       </c>
       <c r="D188" s="4">
+        <v>4</v>
+      </c>
+      <c r="E188" s="4">
         <v>2</v>
       </c>
-      <c r="E188" s="6" t="inlineStr">
+      <c r="F188" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12529,9 +13096,12 @@
         </is>
       </c>
       <c r="D189" s="4">
+        <v>4</v>
+      </c>
+      <c r="E189" s="4">
         <v>3</v>
       </c>
-      <c r="E189" s="6" t="inlineStr">
+      <c r="F189" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12585,9 +13155,12 @@
         </is>
       </c>
       <c r="D190" s="4">
+        <v>2</v>
+      </c>
+      <c r="E190" s="4">
         <v>1</v>
       </c>
-      <c r="E190" s="6" t="inlineStr">
+      <c r="F190" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12641,9 +13214,12 @@
         </is>
       </c>
       <c r="D191" s="4">
+        <v>3</v>
+      </c>
+      <c r="E191" s="4">
         <v>1</v>
       </c>
-      <c r="E191" s="6" t="inlineStr">
+      <c r="F191" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12697,9 +13273,12 @@
         </is>
       </c>
       <c r="D192" s="4">
+        <v>3</v>
+      </c>
+      <c r="E192" s="4">
         <v>2</v>
       </c>
-      <c r="E192" s="6" t="inlineStr">
+      <c r="F192" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12755,7 +13334,10 @@
       <c r="D193" s="4">
         <v>1</v>
       </c>
-      <c r="E193" s="6" t="inlineStr">
+      <c r="E193" s="4">
+        <v>1</v>
+      </c>
+      <c r="F193" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12816,9 +13398,12 @@
         </is>
       </c>
       <c r="D194" s="4">
+        <v>3</v>
+      </c>
+      <c r="E194" s="4">
         <v>1</v>
       </c>
-      <c r="E194" s="6" t="inlineStr">
+      <c r="F194" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -12844,9 +13429,12 @@
         </is>
       </c>
       <c r="D195" s="4">
+        <v>2</v>
+      </c>
+      <c r="E195" s="4">
         <v>1</v>
       </c>
-      <c r="E195" s="6" t="inlineStr">
+      <c r="F195" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12924,7 +13512,10 @@
       <c r="D196" s="4">
         <v>2</v>
       </c>
-      <c r="E196" s="6" t="inlineStr">
+      <c r="E196" s="4">
+        <v>2</v>
+      </c>
+      <c r="F196" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13002,7 +13593,10 @@
       <c r="D197" s="4">
         <v>1</v>
       </c>
-      <c r="E197" s="6" t="inlineStr">
+      <c r="E197" s="4">
+        <v>1</v>
+      </c>
+      <c r="F197" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13095,7 +13689,10 @@
       <c r="D198" s="4">
         <v>1</v>
       </c>
-      <c r="E198" s="6" t="inlineStr">
+      <c r="E198" s="4">
+        <v>1</v>
+      </c>
+      <c r="F198" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13196,7 +13793,10 @@
       <c r="D199" s="4">
         <v>1</v>
       </c>
-      <c r="E199" s="6" t="inlineStr">
+      <c r="E199" s="4">
+        <v>1</v>
+      </c>
+      <c r="F199" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -13224,7 +13824,10 @@
       <c r="D200" s="4">
         <v>1</v>
       </c>
-      <c r="E200" s="6" t="inlineStr">
+      <c r="E200" s="4">
+        <v>1</v>
+      </c>
+      <c r="F200" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13330,9 +13933,12 @@
         </is>
       </c>
       <c r="D201" s="4">
+        <v>2</v>
+      </c>
+      <c r="E201" s="4">
         <v>1</v>
       </c>
-      <c r="E201" s="6" t="inlineStr">
+      <c r="F201" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13438,9 +14044,12 @@
         </is>
       </c>
       <c r="D202" s="4">
+        <v>2</v>
+      </c>
+      <c r="E202" s="4">
         <v>1</v>
       </c>
-      <c r="E202" s="6" t="inlineStr">
+      <c r="F202" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13548,7 +14157,10 @@
       <c r="D203" s="4">
         <v>1</v>
       </c>
-      <c r="E203" s="6" t="inlineStr">
+      <c r="E203" s="4">
+        <v>1</v>
+      </c>
+      <c r="F203" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -13574,9 +14186,12 @@
         </is>
       </c>
       <c r="D204" s="4">
+        <v>2</v>
+      </c>
+      <c r="E204" s="4">
         <v>1</v>
       </c>
-      <c r="E204" s="6" t="inlineStr">
+      <c r="F204" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -13602,9 +14217,12 @@
         </is>
       </c>
       <c r="D205" s="4">
+        <v>4</v>
+      </c>
+      <c r="E205" s="4">
         <v>1</v>
       </c>
-      <c r="E205" s="6" t="inlineStr">
+      <c r="F205" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13725,9 +14343,12 @@
         </is>
       </c>
       <c r="D206" s="4">
+        <v>4</v>
+      </c>
+      <c r="E206" s="4">
         <v>2</v>
       </c>
-      <c r="E206" s="6" t="inlineStr">
+      <c r="F206" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13848,9 +14469,12 @@
         </is>
       </c>
       <c r="D207" s="4">
+        <v>4</v>
+      </c>
+      <c r="E207" s="4">
         <v>3</v>
       </c>
-      <c r="E207" s="6" t="inlineStr">
+      <c r="F207" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13973,7 +14597,10 @@
       <c r="D208" s="4">
         <v>1</v>
       </c>
-      <c r="E208" s="6" t="inlineStr">
+      <c r="E208" s="4">
+        <v>1</v>
+      </c>
+      <c r="F208" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -14001,7 +14628,10 @@
       <c r="D209" s="4">
         <v>1</v>
       </c>
-      <c r="E209" s="6" t="inlineStr">
+      <c r="E209" s="4">
+        <v>1</v>
+      </c>
+      <c r="F209" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -14029,7 +14659,10 @@
       <c r="D210" s="4">
         <v>1</v>
       </c>
-      <c r="E210" s="6" t="inlineStr">
+      <c r="E210" s="4">
+        <v>1</v>
+      </c>
+      <c r="F210" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14083,9 +14716,12 @@
         </is>
       </c>
       <c r="D211" s="4">
+        <v>2</v>
+      </c>
+      <c r="E211" s="4">
         <v>1</v>
       </c>
-      <c r="E211" s="6" t="inlineStr">
+      <c r="F211" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14148,7 +14784,10 @@
       <c r="D212" s="4">
         <v>1</v>
       </c>
-      <c r="E212" s="6" t="inlineStr">
+      <c r="E212" s="4">
+        <v>1</v>
+      </c>
+      <c r="F212" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14219,7 +14858,10 @@
       <c r="D213" s="4">
         <v>1</v>
       </c>
-      <c r="E213" s="6" t="inlineStr">
+      <c r="E213" s="4">
+        <v>1</v>
+      </c>
+      <c r="F213" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -14247,7 +14889,10 @@
       <c r="D214" s="4">
         <v>1</v>
       </c>
-      <c r="E214" s="6" t="inlineStr">
+      <c r="E214" s="4">
+        <v>1</v>
+      </c>
+      <c r="F214" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -14273,9 +14918,12 @@
         </is>
       </c>
       <c r="D215" s="4">
+        <v>2</v>
+      </c>
+      <c r="E215" s="4">
         <v>1</v>
       </c>
-      <c r="E215" s="6" t="inlineStr">
+      <c r="F215" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -14303,7 +14951,10 @@
       <c r="D216" s="4">
         <v>1</v>
       </c>
-      <c r="E216" s="6" t="inlineStr">
+      <c r="E216" s="4">
+        <v>1</v>
+      </c>
+      <c r="F216" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14411,7 +15062,10 @@
       <c r="D217" s="4">
         <v>1</v>
       </c>
-      <c r="E217" s="6" t="inlineStr">
+      <c r="E217" s="4">
+        <v>1</v>
+      </c>
+      <c r="F217" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -14439,7 +15093,10 @@
       <c r="D218" s="4">
         <v>1</v>
       </c>
-      <c r="E218" s="6" t="inlineStr">
+      <c r="E218" s="4">
+        <v>1</v>
+      </c>
+      <c r="F218" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -14467,7 +15124,10 @@
       <c r="D219" s="4">
         <v>1</v>
       </c>
-      <c r="E219" s="6" t="inlineStr">
+      <c r="E219" s="4">
+        <v>1</v>
+      </c>
+      <c r="F219" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -14493,9 +15153,12 @@
         </is>
       </c>
       <c r="D220" s="4">
+        <v>2</v>
+      </c>
+      <c r="E220" s="4">
         <v>1</v>
       </c>
-      <c r="E220" s="6" t="inlineStr">
+      <c r="F220" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14611,7 +15274,10 @@
       <c r="D221" s="4">
         <v>1</v>
       </c>
-      <c r="E221" s="6" t="inlineStr">
+      <c r="E221" s="4">
+        <v>1</v>
+      </c>
+      <c r="F221" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14732,9 +15398,12 @@
         </is>
       </c>
       <c r="D222" s="4">
+        <v>2</v>
+      </c>
+      <c r="E222" s="4">
         <v>1</v>
       </c>
-      <c r="E222" s="6" t="inlineStr">
+      <c r="F222" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14788,9 +15457,12 @@
         </is>
       </c>
       <c r="D223" s="4">
+        <v>2</v>
+      </c>
+      <c r="E223" s="4">
         <v>1</v>
       </c>
-      <c r="E223" s="6" t="inlineStr">
+      <c r="F223" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14846,7 +15518,10 @@
       <c r="D224" s="4">
         <v>2</v>
       </c>
-      <c r="E224" s="6" t="inlineStr">
+      <c r="E224" s="4">
+        <v>2</v>
+      </c>
+      <c r="F224" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14902,7 +15577,10 @@
       <c r="D225" s="4">
         <v>1</v>
       </c>
-      <c r="E225" s="6" t="inlineStr">
+      <c r="E225" s="4">
+        <v>1</v>
+      </c>
+      <c r="F225" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -14930,7 +15608,10 @@
       <c r="D226" s="4">
         <v>1</v>
       </c>
-      <c r="E226" s="6" t="inlineStr">
+      <c r="E226" s="4">
+        <v>1</v>
+      </c>
+      <c r="F226" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -14956,9 +15637,12 @@
         </is>
       </c>
       <c r="D227" s="4">
+        <v>2</v>
+      </c>
+      <c r="E227" s="4">
         <v>1</v>
       </c>
-      <c r="E227" s="6" t="inlineStr">
+      <c r="F227" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15036,7 +15720,10 @@
       <c r="D228" s="4">
         <v>1</v>
       </c>
-      <c r="E228" s="6" t="inlineStr">
+      <c r="E228" s="4">
+        <v>1</v>
+      </c>
+      <c r="F228" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15127,9 +15814,12 @@
         </is>
       </c>
       <c r="D229" s="4">
+        <v>2</v>
+      </c>
+      <c r="E229" s="4">
         <v>1</v>
       </c>
-      <c r="E229" s="6" t="inlineStr">
+      <c r="F229" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15230,7 +15920,10 @@
       <c r="D230" s="4">
         <v>1</v>
       </c>
-      <c r="E230" s="6" t="inlineStr">
+      <c r="E230" s="4">
+        <v>1</v>
+      </c>
+      <c r="F230" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -15258,7 +15951,10 @@
       <c r="D231" s="4">
         <v>1</v>
       </c>
-      <c r="E231" s="6" t="inlineStr">
+      <c r="E231" s="4">
+        <v>1</v>
+      </c>
+      <c r="F231" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15359,7 +16055,10 @@
       <c r="D232" s="4">
         <v>1</v>
       </c>
-      <c r="E232" s="6" t="inlineStr">
+      <c r="E232" s="4">
+        <v>1</v>
+      </c>
+      <c r="F232" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -15385,9 +16084,12 @@
         </is>
       </c>
       <c r="D233" s="4">
+        <v>4</v>
+      </c>
+      <c r="E233" s="4">
         <v>1</v>
       </c>
-      <c r="E233" s="6" t="inlineStr">
+      <c r="F233" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15493,9 +16195,12 @@
         </is>
       </c>
       <c r="D234" s="4">
+        <v>4</v>
+      </c>
+      <c r="E234" s="4">
         <v>2</v>
       </c>
-      <c r="E234" s="6" t="inlineStr">
+      <c r="F234" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15601,9 +16306,12 @@
         </is>
       </c>
       <c r="D235" s="4">
+        <v>2</v>
+      </c>
+      <c r="E235" s="4">
         <v>1</v>
       </c>
-      <c r="E235" s="6" t="inlineStr">
+      <c r="F235" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -15631,7 +16339,10 @@
       <c r="D236" s="4">
         <v>1</v>
       </c>
-      <c r="E236" s="6" t="inlineStr">
+      <c r="E236" s="4">
+        <v>1</v>
+      </c>
+      <c r="F236" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -15657,9 +16368,12 @@
         </is>
       </c>
       <c r="D237" s="4">
+        <v>7</v>
+      </c>
+      <c r="E237" s="4">
         <v>1</v>
       </c>
-      <c r="E237" s="6" t="inlineStr">
+      <c r="F237" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15713,9 +16427,12 @@
         </is>
       </c>
       <c r="D238" s="4">
+        <v>7</v>
+      </c>
+      <c r="E238" s="4">
         <v>2</v>
       </c>
-      <c r="E238" s="6" t="inlineStr">
+      <c r="F238" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15769,9 +16486,12 @@
         </is>
       </c>
       <c r="D239" s="4">
+        <v>7</v>
+      </c>
+      <c r="E239" s="4">
         <v>3</v>
       </c>
-      <c r="E239" s="6" t="inlineStr">
+      <c r="F239" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15825,9 +16545,12 @@
         </is>
       </c>
       <c r="D240" s="4">
+        <v>7</v>
+      </c>
+      <c r="E240" s="4">
         <v>4</v>
       </c>
-      <c r="E240" s="6" t="inlineStr">
+      <c r="F240" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15881,9 +16604,12 @@
         </is>
       </c>
       <c r="D241" s="4">
+        <v>7</v>
+      </c>
+      <c r="E241" s="4">
         <v>5</v>
       </c>
-      <c r="E241" s="6" t="inlineStr">
+      <c r="F241" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15937,9 +16663,12 @@
         </is>
       </c>
       <c r="D242" s="4">
+        <v>7</v>
+      </c>
+      <c r="E242" s="4">
         <v>6</v>
       </c>
-      <c r="E242" s="6" t="inlineStr">
+      <c r="F242" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15995,7 +16724,10 @@
       <c r="D243" s="4">
         <v>7</v>
       </c>
-      <c r="E243" s="6" t="inlineStr">
+      <c r="E243" s="4">
+        <v>7</v>
+      </c>
+      <c r="F243" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16049,9 +16781,12 @@
         </is>
       </c>
       <c r="D244" s="4">
+        <v>4</v>
+      </c>
+      <c r="E244" s="4">
         <v>1</v>
       </c>
-      <c r="E244" s="6" t="inlineStr">
+      <c r="F244" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16105,9 +16840,12 @@
         </is>
       </c>
       <c r="D245" s="4">
+        <v>4</v>
+      </c>
+      <c r="E245" s="4">
         <v>2</v>
       </c>
-      <c r="E245" s="6" t="inlineStr">
+      <c r="F245" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16161,9 +16899,12 @@
         </is>
       </c>
       <c r="D246" s="4">
+        <v>4</v>
+      </c>
+      <c r="E246" s="4">
         <v>3</v>
       </c>
-      <c r="E246" s="6" t="inlineStr">
+      <c r="F246" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16219,7 +16960,10 @@
       <c r="D247" s="4">
         <v>4</v>
       </c>
-      <c r="E247" s="6" t="inlineStr">
+      <c r="E247" s="4">
+        <v>4</v>
+      </c>
+      <c r="F247" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16275,7 +17019,10 @@
       <c r="D248" s="4">
         <v>1</v>
       </c>
-      <c r="E248" s="6" t="inlineStr">
+      <c r="E248" s="4">
+        <v>1</v>
+      </c>
+      <c r="F248" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16329,9 +17076,12 @@
         </is>
       </c>
       <c r="D249" s="4">
+        <v>6</v>
+      </c>
+      <c r="E249" s="4">
         <v>1</v>
       </c>
-      <c r="E249" s="6" t="inlineStr">
+      <c r="F249" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16385,9 +17135,12 @@
         </is>
       </c>
       <c r="D250" s="4">
+        <v>6</v>
+      </c>
+      <c r="E250" s="4">
         <v>2</v>
       </c>
-      <c r="E250" s="6" t="inlineStr">
+      <c r="F250" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16441,9 +17194,12 @@
         </is>
       </c>
       <c r="D251" s="4">
+        <v>6</v>
+      </c>
+      <c r="E251" s="4">
         <v>3</v>
       </c>
-      <c r="E251" s="6" t="inlineStr">
+      <c r="F251" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16497,9 +17253,12 @@
         </is>
       </c>
       <c r="D252" s="4">
+        <v>6</v>
+      </c>
+      <c r="E252" s="4">
         <v>4</v>
       </c>
-      <c r="E252" s="6" t="inlineStr">
+      <c r="F252" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16553,9 +17312,12 @@
         </is>
       </c>
       <c r="D253" s="4">
+        <v>6</v>
+      </c>
+      <c r="E253" s="4">
         <v>5</v>
       </c>
-      <c r="E253" s="6" t="inlineStr">
+      <c r="F253" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16611,7 +17373,10 @@
       <c r="D254" s="4">
         <v>1</v>
       </c>
-      <c r="E254" s="6" t="inlineStr">
+      <c r="E254" s="4">
+        <v>1</v>
+      </c>
+      <c r="F254" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16667,7 +17432,10 @@
       <c r="D255" s="4">
         <v>1</v>
       </c>
-      <c r="E255" s="6" t="inlineStr">
+      <c r="E255" s="4">
+        <v>1</v>
+      </c>
+      <c r="F255" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16723,7 +17491,10 @@
       <c r="D256" s="4">
         <v>1</v>
       </c>
-      <c r="E256" s="6" t="inlineStr">
+      <c r="E256" s="4">
+        <v>1</v>
+      </c>
+      <c r="F256" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16777,9 +17548,12 @@
         </is>
       </c>
       <c r="D257" s="4">
+        <v>3</v>
+      </c>
+      <c r="E257" s="4">
         <v>1</v>
       </c>
-      <c r="E257" s="6" t="inlineStr">
+      <c r="F257" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16833,9 +17607,12 @@
         </is>
       </c>
       <c r="D258" s="4">
+        <v>3</v>
+      </c>
+      <c r="E258" s="4">
         <v>2</v>
       </c>
-      <c r="E258" s="6" t="inlineStr">
+      <c r="F258" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16891,7 +17668,10 @@
       <c r="D259" s="4">
         <v>3</v>
       </c>
-      <c r="E259" s="6" t="inlineStr">
+      <c r="E259" s="4">
+        <v>3</v>
+      </c>
+      <c r="F259" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16945,9 +17725,12 @@
         </is>
       </c>
       <c r="D260" s="4">
+        <v>17</v>
+      </c>
+      <c r="E260" s="4">
         <v>1</v>
       </c>
-      <c r="E260" s="6" t="inlineStr">
+      <c r="F260" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17001,9 +17784,12 @@
         </is>
       </c>
       <c r="D261" s="4">
+        <v>17</v>
+      </c>
+      <c r="E261" s="4">
         <v>2</v>
       </c>
-      <c r="E261" s="6" t="inlineStr">
+      <c r="F261" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17057,9 +17843,12 @@
         </is>
       </c>
       <c r="D262" s="4">
+        <v>17</v>
+      </c>
+      <c r="E262" s="4">
         <v>3</v>
       </c>
-      <c r="E262" s="6" t="inlineStr">
+      <c r="F262" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17113,9 +17902,12 @@
         </is>
       </c>
       <c r="D263" s="4">
+        <v>17</v>
+      </c>
+      <c r="E263" s="4">
         <v>4</v>
       </c>
-      <c r="E263" s="6" t="inlineStr">
+      <c r="F263" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17169,9 +17961,12 @@
         </is>
       </c>
       <c r="D264" s="4">
+        <v>17</v>
+      </c>
+      <c r="E264" s="4">
         <v>5</v>
       </c>
-      <c r="E264" s="6" t="inlineStr">
+      <c r="F264" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17225,9 +18020,12 @@
         </is>
       </c>
       <c r="D265" s="4">
+        <v>17</v>
+      </c>
+      <c r="E265" s="4">
         <v>6</v>
       </c>
-      <c r="E265" s="6" t="inlineStr">
+      <c r="F265" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17281,9 +18079,12 @@
         </is>
       </c>
       <c r="D266" s="4">
+        <v>17</v>
+      </c>
+      <c r="E266" s="4">
         <v>7</v>
       </c>
-      <c r="E266" s="6" t="inlineStr">
+      <c r="F266" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17337,9 +18138,12 @@
         </is>
       </c>
       <c r="D267" s="4">
+        <v>17</v>
+      </c>
+      <c r="E267" s="4">
         <v>8</v>
       </c>
-      <c r="E267" s="6" t="inlineStr">
+      <c r="F267" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17393,9 +18197,12 @@
         </is>
       </c>
       <c r="D268" s="4">
+        <v>17</v>
+      </c>
+      <c r="E268" s="4">
         <v>9</v>
       </c>
-      <c r="E268" s="6" t="inlineStr">
+      <c r="F268" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17449,9 +18256,12 @@
         </is>
       </c>
       <c r="D269" s="4">
+        <v>17</v>
+      </c>
+      <c r="E269" s="4">
         <v>10</v>
       </c>
-      <c r="E269" s="6" t="inlineStr">
+      <c r="F269" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17505,9 +18315,12 @@
         </is>
       </c>
       <c r="D270" s="4">
+        <v>17</v>
+      </c>
+      <c r="E270" s="4">
         <v>11</v>
       </c>
-      <c r="E270" s="6" t="inlineStr">
+      <c r="F270" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17561,9 +18374,12 @@
         </is>
       </c>
       <c r="D271" s="4">
+        <v>17</v>
+      </c>
+      <c r="E271" s="4">
         <v>12</v>
       </c>
-      <c r="E271" s="6" t="inlineStr">
+      <c r="F271" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17617,9 +18433,12 @@
         </is>
       </c>
       <c r="D272" s="4">
+        <v>17</v>
+      </c>
+      <c r="E272" s="4">
         <v>13</v>
       </c>
-      <c r="E272" s="6" t="inlineStr">
+      <c r="F272" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17673,9 +18492,12 @@
         </is>
       </c>
       <c r="D273" s="4">
+        <v>17</v>
+      </c>
+      <c r="E273" s="4">
         <v>14</v>
       </c>
-      <c r="E273" s="6" t="inlineStr">
+      <c r="F273" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17729,9 +18551,12 @@
         </is>
       </c>
       <c r="D274" s="4">
+        <v>17</v>
+      </c>
+      <c r="E274" s="4">
         <v>15</v>
       </c>
-      <c r="E274" s="6" t="inlineStr">
+      <c r="F274" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17785,9 +18610,12 @@
         </is>
       </c>
       <c r="D275" s="4">
+        <v>17</v>
+      </c>
+      <c r="E275" s="4">
         <v>16</v>
       </c>
-      <c r="E275" s="6" t="inlineStr">
+      <c r="F275" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17843,7 +18671,10 @@
       <c r="D276" s="4">
         <v>17</v>
       </c>
-      <c r="E276" s="6" t="inlineStr">
+      <c r="E276" s="4">
+        <v>17</v>
+      </c>
+      <c r="F276" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17897,9 +18728,12 @@
         </is>
       </c>
       <c r="D277" s="4">
+        <v>7</v>
+      </c>
+      <c r="E277" s="4">
         <v>1</v>
       </c>
-      <c r="E277" s="6" t="inlineStr">
+      <c r="F277" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17953,9 +18787,12 @@
         </is>
       </c>
       <c r="D278" s="4">
+        <v>7</v>
+      </c>
+      <c r="E278" s="4">
         <v>2</v>
       </c>
-      <c r="E278" s="6" t="inlineStr">
+      <c r="F278" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18009,9 +18846,12 @@
         </is>
       </c>
       <c r="D279" s="4">
+        <v>7</v>
+      </c>
+      <c r="E279" s="4">
         <v>3</v>
       </c>
-      <c r="E279" s="6" t="inlineStr">
+      <c r="F279" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18065,9 +18905,12 @@
         </is>
       </c>
       <c r="D280" s="4">
+        <v>7</v>
+      </c>
+      <c r="E280" s="4">
         <v>4</v>
       </c>
-      <c r="E280" s="6" t="inlineStr">
+      <c r="F280" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18121,9 +18964,12 @@
         </is>
       </c>
       <c r="D281" s="4">
+        <v>7</v>
+      </c>
+      <c r="E281" s="4">
         <v>5</v>
       </c>
-      <c r="E281" s="6" t="inlineStr">
+      <c r="F281" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18177,9 +19023,12 @@
         </is>
       </c>
       <c r="D282" s="4">
+        <v>7</v>
+      </c>
+      <c r="E282" s="4">
         <v>6</v>
       </c>
-      <c r="E282" s="6" t="inlineStr">
+      <c r="F282" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18235,7 +19084,10 @@
       <c r="D283" s="4">
         <v>7</v>
       </c>
-      <c r="E283" s="6" t="inlineStr">
+      <c r="E283" s="4">
+        <v>7</v>
+      </c>
+      <c r="F283" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18289,9 +19141,12 @@
         </is>
       </c>
       <c r="D284" s="4">
+        <v>4</v>
+      </c>
+      <c r="E284" s="4">
         <v>1</v>
       </c>
-      <c r="E284" s="6" t="inlineStr">
+      <c r="F284" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18345,9 +19200,12 @@
         </is>
       </c>
       <c r="D285" s="4">
+        <v>4</v>
+      </c>
+      <c r="E285" s="4">
         <v>2</v>
       </c>
-      <c r="E285" s="6" t="inlineStr">
+      <c r="F285" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18401,9 +19259,12 @@
         </is>
       </c>
       <c r="D286" s="4">
+        <v>4</v>
+      </c>
+      <c r="E286" s="4">
         <v>3</v>
       </c>
-      <c r="E286" s="6" t="inlineStr">
+      <c r="F286" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18459,7 +19320,10 @@
       <c r="D287" s="4">
         <v>4</v>
       </c>
-      <c r="E287" s="6" t="inlineStr">
+      <c r="E287" s="4">
+        <v>4</v>
+      </c>
+      <c r="F287" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18513,9 +19377,12 @@
         </is>
       </c>
       <c r="D288" s="4">
+        <v>9</v>
+      </c>
+      <c r="E288" s="4">
         <v>1</v>
       </c>
-      <c r="E288" s="6" t="inlineStr">
+      <c r="F288" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18569,9 +19436,12 @@
         </is>
       </c>
       <c r="D289" s="4">
+        <v>9</v>
+      </c>
+      <c r="E289" s="4">
         <v>2</v>
       </c>
-      <c r="E289" s="6" t="inlineStr">
+      <c r="F289" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18625,9 +19495,12 @@
         </is>
       </c>
       <c r="D290" s="4">
+        <v>9</v>
+      </c>
+      <c r="E290" s="4">
         <v>3</v>
       </c>
-      <c r="E290" s="6" t="inlineStr">
+      <c r="F290" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18681,9 +19554,12 @@
         </is>
       </c>
       <c r="D291" s="4">
+        <v>9</v>
+      </c>
+      <c r="E291" s="4">
         <v>4</v>
       </c>
-      <c r="E291" s="6" t="inlineStr">
+      <c r="F291" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18737,9 +19613,12 @@
         </is>
       </c>
       <c r="D292" s="4">
+        <v>9</v>
+      </c>
+      <c r="E292" s="4">
         <v>5</v>
       </c>
-      <c r="E292" s="6" t="inlineStr">
+      <c r="F292" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18793,9 +19672,12 @@
         </is>
       </c>
       <c r="D293" s="4">
+        <v>9</v>
+      </c>
+      <c r="E293" s="4">
         <v>6</v>
       </c>
-      <c r="E293" s="6" t="inlineStr">
+      <c r="F293" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18849,9 +19731,12 @@
         </is>
       </c>
       <c r="D294" s="4">
+        <v>9</v>
+      </c>
+      <c r="E294" s="4">
         <v>7</v>
       </c>
-      <c r="E294" s="6" t="inlineStr">
+      <c r="F294" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18905,9 +19790,12 @@
         </is>
       </c>
       <c r="D295" s="4">
+        <v>9</v>
+      </c>
+      <c r="E295" s="4">
         <v>8</v>
       </c>
-      <c r="E295" s="6" t="inlineStr">
+      <c r="F295" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18961,9 +19849,12 @@
         </is>
       </c>
       <c r="D296" s="4">
+        <v>5</v>
+      </c>
+      <c r="E296" s="4">
         <v>1</v>
       </c>
-      <c r="E296" s="6" t="inlineStr">
+      <c r="F296" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19017,9 +19908,12 @@
         </is>
       </c>
       <c r="D297" s="4">
+        <v>5</v>
+      </c>
+      <c r="E297" s="4">
         <v>2</v>
       </c>
-      <c r="E297" s="6" t="inlineStr">
+      <c r="F297" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19073,9 +19967,12 @@
         </is>
       </c>
       <c r="D298" s="4">
+        <v>5</v>
+      </c>
+      <c r="E298" s="4">
         <v>3</v>
       </c>
-      <c r="E298" s="6" t="inlineStr">
+      <c r="F298" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19129,9 +20026,12 @@
         </is>
       </c>
       <c r="D299" s="4">
+        <v>5</v>
+      </c>
+      <c r="E299" s="4">
         <v>4</v>
       </c>
-      <c r="E299" s="6" t="inlineStr">
+      <c r="F299" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19187,7 +20087,10 @@
       <c r="D300" s="4">
         <v>5</v>
       </c>
-      <c r="E300" s="6" t="inlineStr">
+      <c r="E300" s="4">
+        <v>5</v>
+      </c>
+      <c r="F300" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19241,9 +20144,12 @@
         </is>
       </c>
       <c r="D301" s="4">
+        <v>5</v>
+      </c>
+      <c r="E301" s="4">
         <v>1</v>
       </c>
-      <c r="E301" s="6" t="inlineStr">
+      <c r="F301" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19297,9 +20203,12 @@
         </is>
       </c>
       <c r="D302" s="4">
+        <v>5</v>
+      </c>
+      <c r="E302" s="4">
         <v>2</v>
       </c>
-      <c r="E302" s="6" t="inlineStr">
+      <c r="F302" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19353,9 +20262,12 @@
         </is>
       </c>
       <c r="D303" s="4">
+        <v>5</v>
+      </c>
+      <c r="E303" s="4">
         <v>3</v>
       </c>
-      <c r="E303" s="6" t="inlineStr">
+      <c r="F303" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19409,9 +20321,12 @@
         </is>
       </c>
       <c r="D304" s="4">
+        <v>5</v>
+      </c>
+      <c r="E304" s="4">
         <v>4</v>
       </c>
-      <c r="E304" s="6" t="inlineStr">
+      <c r="F304" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19467,7 +20382,10 @@
       <c r="D305" s="4">
         <v>5</v>
       </c>
-      <c r="E305" s="6" t="inlineStr">
+      <c r="E305" s="4">
+        <v>5</v>
+      </c>
+      <c r="F305" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19521,9 +20439,12 @@
         </is>
       </c>
       <c r="D306" s="4">
+        <v>4</v>
+      </c>
+      <c r="E306" s="4">
         <v>1</v>
       </c>
-      <c r="E306" s="6" t="inlineStr">
+      <c r="F306" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19577,9 +20498,12 @@
         </is>
       </c>
       <c r="D307" s="4">
+        <v>4</v>
+      </c>
+      <c r="E307" s="4">
         <v>2</v>
       </c>
-      <c r="E307" s="6" t="inlineStr">
+      <c r="F307" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19633,9 +20557,12 @@
         </is>
       </c>
       <c r="D308" s="4">
+        <v>4</v>
+      </c>
+      <c r="E308" s="4">
         <v>3</v>
       </c>
-      <c r="E308" s="6" t="inlineStr">
+      <c r="F308" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19691,7 +20618,10 @@
       <c r="D309" s="4">
         <v>4</v>
       </c>
-      <c r="E309" s="6" t="inlineStr">
+      <c r="E309" s="4">
+        <v>4</v>
+      </c>
+      <c r="F309" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19745,9 +20675,12 @@
         </is>
       </c>
       <c r="D310" s="4">
+        <v>3</v>
+      </c>
+      <c r="E310" s="4">
         <v>1</v>
       </c>
-      <c r="E310" s="6" t="inlineStr">
+      <c r="F310" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19801,9 +20734,12 @@
         </is>
       </c>
       <c r="D311" s="4">
+        <v>3</v>
+      </c>
+      <c r="E311" s="4">
         <v>2</v>
       </c>
-      <c r="E311" s="6" t="inlineStr">
+      <c r="F311" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19859,7 +20795,10 @@
       <c r="D312" s="4">
         <v>3</v>
       </c>
-      <c r="E312" s="6" t="inlineStr">
+      <c r="E312" s="4">
+        <v>3</v>
+      </c>
+      <c r="F312" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19913,9 +20852,12 @@
         </is>
       </c>
       <c r="D313" s="4">
+        <v>5</v>
+      </c>
+      <c r="E313" s="4">
         <v>1</v>
       </c>
-      <c r="E313" s="6" t="inlineStr">
+      <c r="F313" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19969,9 +20911,12 @@
         </is>
       </c>
       <c r="D314" s="4">
+        <v>5</v>
+      </c>
+      <c r="E314" s="4">
         <v>2</v>
       </c>
-      <c r="E314" s="6" t="inlineStr">
+      <c r="F314" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20025,9 +20970,12 @@
         </is>
       </c>
       <c r="D315" s="4">
+        <v>5</v>
+      </c>
+      <c r="E315" s="4">
         <v>3</v>
       </c>
-      <c r="E315" s="6" t="inlineStr">
+      <c r="F315" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20081,9 +21029,12 @@
         </is>
       </c>
       <c r="D316" s="4">
+        <v>5</v>
+      </c>
+      <c r="E316" s="4">
         <v>4</v>
       </c>
-      <c r="E316" s="6" t="inlineStr">
+      <c r="F316" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20139,7 +21090,10 @@
       <c r="D317" s="4">
         <v>5</v>
       </c>
-      <c r="E317" s="6" t="inlineStr">
+      <c r="E317" s="4">
+        <v>5</v>
+      </c>
+      <c r="F317" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20193,9 +21147,12 @@
         </is>
       </c>
       <c r="D318" s="4">
+        <v>47</v>
+      </c>
+      <c r="E318" s="4">
         <v>1</v>
       </c>
-      <c r="E318" s="6" t="inlineStr">
+      <c r="F318" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20249,9 +21206,12 @@
         </is>
       </c>
       <c r="D319" s="4">
+        <v>47</v>
+      </c>
+      <c r="E319" s="4">
         <v>2</v>
       </c>
-      <c r="E319" s="6" t="inlineStr">
+      <c r="F319" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20305,9 +21265,12 @@
         </is>
       </c>
       <c r="D320" s="4">
+        <v>47</v>
+      </c>
+      <c r="E320" s="4">
         <v>3</v>
       </c>
-      <c r="E320" s="6" t="inlineStr">
+      <c r="F320" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20361,9 +21324,12 @@
         </is>
       </c>
       <c r="D321" s="4">
+        <v>47</v>
+      </c>
+      <c r="E321" s="4">
         <v>4</v>
       </c>
-      <c r="E321" s="6" t="inlineStr">
+      <c r="F321" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20417,9 +21383,12 @@
         </is>
       </c>
       <c r="D322" s="4">
+        <v>47</v>
+      </c>
+      <c r="E322" s="4">
         <v>5</v>
       </c>
-      <c r="E322" s="6" t="inlineStr">
+      <c r="F322" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20473,9 +21442,12 @@
         </is>
       </c>
       <c r="D323" s="4">
+        <v>47</v>
+      </c>
+      <c r="E323" s="4">
         <v>6</v>
       </c>
-      <c r="E323" s="6" t="inlineStr">
+      <c r="F323" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20529,9 +21501,12 @@
         </is>
       </c>
       <c r="D324" s="4">
+        <v>47</v>
+      </c>
+      <c r="E324" s="4">
         <v>7</v>
       </c>
-      <c r="E324" s="6" t="inlineStr">
+      <c r="F324" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20585,9 +21560,12 @@
         </is>
       </c>
       <c r="D325" s="4">
+        <v>47</v>
+      </c>
+      <c r="E325" s="4">
         <v>8</v>
       </c>
-      <c r="E325" s="6" t="inlineStr">
+      <c r="F325" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20641,9 +21619,12 @@
         </is>
       </c>
       <c r="D326" s="4">
+        <v>47</v>
+      </c>
+      <c r="E326" s="4">
         <v>9</v>
       </c>
-      <c r="E326" s="6" t="inlineStr">
+      <c r="F326" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20697,9 +21678,12 @@
         </is>
       </c>
       <c r="D327" s="4">
+        <v>47</v>
+      </c>
+      <c r="E327" s="4">
         <v>10</v>
       </c>
-      <c r="E327" s="6" t="inlineStr">
+      <c r="F327" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20753,9 +21737,12 @@
         </is>
       </c>
       <c r="D328" s="4">
+        <v>47</v>
+      </c>
+      <c r="E328" s="4">
         <v>11</v>
       </c>
-      <c r="E328" s="6" t="inlineStr">
+      <c r="F328" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20809,9 +21796,12 @@
         </is>
       </c>
       <c r="D329" s="4">
+        <v>47</v>
+      </c>
+      <c r="E329" s="4">
         <v>12</v>
       </c>
-      <c r="E329" s="6" t="inlineStr">
+      <c r="F329" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20865,9 +21855,12 @@
         </is>
       </c>
       <c r="D330" s="4">
+        <v>47</v>
+      </c>
+      <c r="E330" s="4">
         <v>13</v>
       </c>
-      <c r="E330" s="6" t="inlineStr">
+      <c r="F330" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20921,9 +21914,12 @@
         </is>
       </c>
       <c r="D331" s="4">
+        <v>47</v>
+      </c>
+      <c r="E331" s="4">
         <v>14</v>
       </c>
-      <c r="E331" s="6" t="inlineStr">
+      <c r="F331" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20977,9 +21973,12 @@
         </is>
       </c>
       <c r="D332" s="4">
+        <v>47</v>
+      </c>
+      <c r="E332" s="4">
         <v>15</v>
       </c>
-      <c r="E332" s="6" t="inlineStr">
+      <c r="F332" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21033,9 +22032,12 @@
         </is>
       </c>
       <c r="D333" s="4">
+        <v>47</v>
+      </c>
+      <c r="E333" s="4">
         <v>16</v>
       </c>
-      <c r="E333" s="6" t="inlineStr">
+      <c r="F333" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21089,9 +22091,12 @@
         </is>
       </c>
       <c r="D334" s="4">
+        <v>47</v>
+      </c>
+      <c r="E334" s="4">
         <v>17</v>
       </c>
-      <c r="E334" s="6" t="inlineStr">
+      <c r="F334" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21145,9 +22150,12 @@
         </is>
       </c>
       <c r="D335" s="4">
+        <v>47</v>
+      </c>
+      <c r="E335" s="4">
         <v>18</v>
       </c>
-      <c r="E335" s="6" t="inlineStr">
+      <c r="F335" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21201,9 +22209,12 @@
         </is>
       </c>
       <c r="D336" s="4">
+        <v>47</v>
+      </c>
+      <c r="E336" s="4">
         <v>19</v>
       </c>
-      <c r="E336" s="6" t="inlineStr">
+      <c r="F336" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21257,9 +22268,12 @@
         </is>
       </c>
       <c r="D337" s="4">
+        <v>47</v>
+      </c>
+      <c r="E337" s="4">
         <v>20</v>
       </c>
-      <c r="E337" s="6" t="inlineStr">
+      <c r="F337" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21313,9 +22327,12 @@
         </is>
       </c>
       <c r="D338" s="4">
+        <v>6</v>
+      </c>
+      <c r="E338" s="4">
         <v>1</v>
       </c>
-      <c r="E338" s="6" t="inlineStr">
+      <c r="F338" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21385,9 +22402,12 @@
         </is>
       </c>
       <c r="D339" s="4">
+        <v>6</v>
+      </c>
+      <c r="E339" s="4">
         <v>2</v>
       </c>
-      <c r="E339" s="6" t="inlineStr">
+      <c r="F339" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21457,9 +22477,12 @@
         </is>
       </c>
       <c r="D340" s="4">
+        <v>6</v>
+      </c>
+      <c r="E340" s="4">
         <v>3</v>
       </c>
-      <c r="E340" s="6" t="inlineStr">
+      <c r="F340" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21529,9 +22552,12 @@
         </is>
       </c>
       <c r="D341" s="4">
+        <v>6</v>
+      </c>
+      <c r="E341" s="4">
         <v>4</v>
       </c>
-      <c r="E341" s="6" t="inlineStr">
+      <c r="F341" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21601,9 +22627,12 @@
         </is>
       </c>
       <c r="D342" s="4">
+        <v>6</v>
+      </c>
+      <c r="E342" s="4">
         <v>5</v>
       </c>
-      <c r="E342" s="6" t="inlineStr">
+      <c r="F342" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21675,7 +22704,10 @@
       <c r="D343" s="4">
         <v>6</v>
       </c>
-      <c r="E343" s="6" t="inlineStr">
+      <c r="E343" s="4">
+        <v>6</v>
+      </c>
+      <c r="F343" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21745,9 +22777,12 @@
         </is>
       </c>
       <c r="D344" s="4">
+        <v>4</v>
+      </c>
+      <c r="E344" s="4">
         <v>1</v>
       </c>
-      <c r="E344" s="6" t="inlineStr">
+      <c r="F344" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21808,9 +22843,12 @@
         </is>
       </c>
       <c r="D345" s="4">
+        <v>4</v>
+      </c>
+      <c r="E345" s="4">
         <v>2</v>
       </c>
-      <c r="E345" s="6" t="inlineStr">
+      <c r="F345" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21871,9 +22909,12 @@
         </is>
       </c>
       <c r="D346" s="4">
+        <v>4</v>
+      </c>
+      <c r="E346" s="4">
         <v>3</v>
       </c>
-      <c r="E346" s="6" t="inlineStr">
+      <c r="F346" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21936,7 +22977,10 @@
       <c r="D347" s="4">
         <v>4</v>
       </c>
-      <c r="E347" s="6" t="inlineStr">
+      <c r="E347" s="4">
+        <v>4</v>
+      </c>
+      <c r="F347" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21999,7 +23043,10 @@
       <c r="D348" s="4">
         <v>1</v>
       </c>
-      <c r="E348" s="6" t="inlineStr">
+      <c r="E348" s="4">
+        <v>1</v>
+      </c>
+      <c r="F348" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22068,9 +23115,12 @@
         </is>
       </c>
       <c r="D349" s="4">
+        <v>10</v>
+      </c>
+      <c r="E349" s="4">
         <v>1</v>
       </c>
-      <c r="E349" s="6" t="inlineStr">
+      <c r="F349" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22131,9 +23181,12 @@
         </is>
       </c>
       <c r="D350" s="4">
+        <v>10</v>
+      </c>
+      <c r="E350" s="4">
         <v>2</v>
       </c>
-      <c r="E350" s="6" t="inlineStr">
+      <c r="F350" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22194,9 +23247,12 @@
         </is>
       </c>
       <c r="D351" s="4">
+        <v>10</v>
+      </c>
+      <c r="E351" s="4">
         <v>3</v>
       </c>
-      <c r="E351" s="6" t="inlineStr">
+      <c r="F351" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22257,9 +23313,12 @@
         </is>
       </c>
       <c r="D352" s="4">
+        <v>10</v>
+      </c>
+      <c r="E352" s="4">
         <v>4</v>
       </c>
-      <c r="E352" s="6" t="inlineStr">
+      <c r="F352" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22320,9 +23379,12 @@
         </is>
       </c>
       <c r="D353" s="4">
+        <v>10</v>
+      </c>
+      <c r="E353" s="4">
         <v>5</v>
       </c>
-      <c r="E353" s="6" t="inlineStr">
+      <c r="F353" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22383,9 +23445,12 @@
         </is>
       </c>
       <c r="D354" s="4">
+        <v>10</v>
+      </c>
+      <c r="E354" s="4">
         <v>6</v>
       </c>
-      <c r="E354" s="6" t="inlineStr">
+      <c r="F354" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22446,9 +23511,12 @@
         </is>
       </c>
       <c r="D355" s="4">
+        <v>10</v>
+      </c>
+      <c r="E355" s="4">
         <v>7</v>
       </c>
-      <c r="E355" s="6" t="inlineStr">
+      <c r="F355" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22509,9 +23577,12 @@
         </is>
       </c>
       <c r="D356" s="4">
+        <v>10</v>
+      </c>
+      <c r="E356" s="4">
         <v>8</v>
       </c>
-      <c r="E356" s="6" t="inlineStr">
+      <c r="F356" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22572,9 +23643,12 @@
         </is>
       </c>
       <c r="D357" s="4">
+        <v>10</v>
+      </c>
+      <c r="E357" s="4">
         <v>9</v>
       </c>
-      <c r="E357" s="6" t="inlineStr">
+      <c r="F357" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22637,7 +23711,10 @@
       <c r="D358" s="4">
         <v>10</v>
       </c>
-      <c r="E358" s="6" t="inlineStr">
+      <c r="E358" s="4">
+        <v>10</v>
+      </c>
+      <c r="F358" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22698,9 +23775,12 @@
         </is>
       </c>
       <c r="D359" s="4">
+        <v>4</v>
+      </c>
+      <c r="E359" s="4">
         <v>1</v>
       </c>
-      <c r="E359" s="6" t="inlineStr">
+      <c r="F359" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22769,9 +23849,12 @@
         </is>
       </c>
       <c r="D360" s="4">
+        <v>4</v>
+      </c>
+      <c r="E360" s="4">
         <v>2</v>
       </c>
-      <c r="E360" s="6" t="inlineStr">
+      <c r="F360" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22840,9 +23923,12 @@
         </is>
       </c>
       <c r="D361" s="4">
+        <v>4</v>
+      </c>
+      <c r="E361" s="4">
         <v>3</v>
       </c>
-      <c r="E361" s="6" t="inlineStr">
+      <c r="F361" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22913,7 +23999,10 @@
       <c r="D362" s="4">
         <v>4</v>
       </c>
-      <c r="E362" s="6" t="inlineStr">
+      <c r="E362" s="4">
+        <v>4</v>
+      </c>
+      <c r="F362" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22982,9 +24071,12 @@
         </is>
       </c>
       <c r="D363" s="4">
+        <v>4</v>
+      </c>
+      <c r="E363" s="4">
         <v>1</v>
       </c>
-      <c r="E363" s="6" t="inlineStr">
+      <c r="F363" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23060,9 +24152,12 @@
         </is>
       </c>
       <c r="D364" s="4">
+        <v>4</v>
+      </c>
+      <c r="E364" s="4">
         <v>2</v>
       </c>
-      <c r="E364" s="6" t="inlineStr">
+      <c r="F364" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23138,9 +24233,12 @@
         </is>
       </c>
       <c r="D365" s="4">
+        <v>4</v>
+      </c>
+      <c r="E365" s="4">
         <v>3</v>
       </c>
-      <c r="E365" s="6" t="inlineStr">
+      <c r="F365" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23218,7 +24316,10 @@
       <c r="D366" s="4">
         <v>4</v>
       </c>
-      <c r="E366" s="6" t="inlineStr">
+      <c r="E366" s="4">
+        <v>4</v>
+      </c>
+      <c r="F366" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23294,9 +24395,12 @@
         </is>
       </c>
       <c r="D367" s="4">
+        <v>4</v>
+      </c>
+      <c r="E367" s="4">
         <v>1</v>
       </c>
-      <c r="E367" s="6" t="inlineStr">
+      <c r="F367" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23395,9 +24499,12 @@
         </is>
       </c>
       <c r="D368" s="4">
+        <v>4</v>
+      </c>
+      <c r="E368" s="4">
         <v>2</v>
       </c>
-      <c r="E368" s="6" t="inlineStr">
+      <c r="F368" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23496,9 +24603,12 @@
         </is>
       </c>
       <c r="D369" s="4">
+        <v>4</v>
+      </c>
+      <c r="E369" s="4">
         <v>3</v>
       </c>
-      <c r="E369" s="6" t="inlineStr">
+      <c r="F369" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23591,7 +24701,10 @@
       <c r="D370" s="4">
         <v>4</v>
       </c>
-      <c r="E370" s="6" t="inlineStr">
+      <c r="E370" s="4">
+        <v>4</v>
+      </c>
+      <c r="F370" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23684,7 +24797,10 @@
       <c r="D371" s="4">
         <v>1</v>
       </c>
-      <c r="E371" s="6" t="inlineStr">
+      <c r="E371" s="4">
+        <v>1</v>
+      </c>
+      <c r="F371" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23754,9 +24870,12 @@
         </is>
       </c>
       <c r="D372" s="4">
+        <v>10</v>
+      </c>
+      <c r="E372" s="4">
         <v>1</v>
       </c>
-      <c r="E372" s="6" t="inlineStr">
+      <c r="F372" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23817,9 +24936,12 @@
         </is>
       </c>
       <c r="D373" s="4">
+        <v>10</v>
+      </c>
+      <c r="E373" s="4">
         <v>2</v>
       </c>
-      <c r="E373" s="6" t="inlineStr">
+      <c r="F373" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23880,9 +25002,12 @@
         </is>
       </c>
       <c r="D374" s="4">
+        <v>10</v>
+      </c>
+      <c r="E374" s="4">
         <v>3</v>
       </c>
-      <c r="E374" s="6" t="inlineStr">
+      <c r="F374" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23943,9 +25068,12 @@
         </is>
       </c>
       <c r="D375" s="4">
+        <v>10</v>
+      </c>
+      <c r="E375" s="4">
         <v>4</v>
       </c>
-      <c r="E375" s="6" t="inlineStr">
+      <c r="F375" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24006,9 +25134,12 @@
         </is>
       </c>
       <c r="D376" s="4">
+        <v>10</v>
+      </c>
+      <c r="E376" s="4">
         <v>5</v>
       </c>
-      <c r="E376" s="6" t="inlineStr">
+      <c r="F376" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24069,9 +25200,12 @@
         </is>
       </c>
       <c r="D377" s="4">
+        <v>10</v>
+      </c>
+      <c r="E377" s="4">
         <v>6</v>
       </c>
-      <c r="E377" s="6" t="inlineStr">
+      <c r="F377" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24132,9 +25266,12 @@
         </is>
       </c>
       <c r="D378" s="4">
+        <v>10</v>
+      </c>
+      <c r="E378" s="4">
         <v>7</v>
       </c>
-      <c r="E378" s="6" t="inlineStr">
+      <c r="F378" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24195,9 +25332,12 @@
         </is>
       </c>
       <c r="D379" s="4">
+        <v>10</v>
+      </c>
+      <c r="E379" s="4">
         <v>8</v>
       </c>
-      <c r="E379" s="6" t="inlineStr">
+      <c r="F379" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24258,9 +25398,12 @@
         </is>
       </c>
       <c r="D380" s="4">
+        <v>10</v>
+      </c>
+      <c r="E380" s="4">
         <v>9</v>
       </c>
-      <c r="E380" s="6" t="inlineStr">
+      <c r="F380" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24321,9 +25464,12 @@
         </is>
       </c>
       <c r="D381" s="4">
+        <v>2</v>
+      </c>
+      <c r="E381" s="4">
         <v>1</v>
       </c>
-      <c r="E381" s="6" t="inlineStr">
+      <c r="F381" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24394,7 +25540,10 @@
       <c r="D382" s="4">
         <v>2</v>
       </c>
-      <c r="E382" s="6" t="inlineStr">
+      <c r="E382" s="4">
+        <v>2</v>
+      </c>
+      <c r="F382" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24463,9 +25612,12 @@
         </is>
       </c>
       <c r="D383" s="4">
+        <v>3</v>
+      </c>
+      <c r="E383" s="4">
         <v>1</v>
       </c>
-      <c r="E383" s="6" t="inlineStr">
+      <c r="F383" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24556,9 +25708,12 @@
         </is>
       </c>
       <c r="D384" s="4">
+        <v>3</v>
+      </c>
+      <c r="E384" s="4">
         <v>2</v>
       </c>
-      <c r="E384" s="6" t="inlineStr">
+      <c r="F384" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24651,7 +25806,10 @@
       <c r="D385" s="4">
         <v>3</v>
       </c>
-      <c r="E385" s="6" t="inlineStr">
+      <c r="E385" s="4">
+        <v>3</v>
+      </c>
+      <c r="F385" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24757,9 +25915,12 @@
         </is>
       </c>
       <c r="D386" s="4">
+        <v>2</v>
+      </c>
+      <c r="E386" s="4">
         <v>1</v>
       </c>
-      <c r="E386" s="6" t="inlineStr">
+      <c r="F386" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24831,7 +25992,10 @@
       <c r="D387" s="4">
         <v>2</v>
       </c>
-      <c r="E387" s="6" t="inlineStr">
+      <c r="E387" s="4">
+        <v>2</v>
+      </c>
+      <c r="F387" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24901,9 +26065,12 @@
         </is>
       </c>
       <c r="D388" s="4">
+        <v>2</v>
+      </c>
+      <c r="E388" s="4">
         <v>1</v>
       </c>
-      <c r="E388" s="6" t="inlineStr">
+      <c r="F388" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24975,7 +26142,10 @@
       <c r="D389" s="4">
         <v>2</v>
       </c>
-      <c r="E389" s="6" t="inlineStr">
+      <c r="E389" s="4">
+        <v>2</v>
+      </c>
+      <c r="F389" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25047,7 +26217,10 @@
       <c r="D390" s="4">
         <v>1</v>
       </c>
-      <c r="E390" s="6" t="inlineStr">
+      <c r="E390" s="4">
+        <v>1</v>
+      </c>
+      <c r="F390" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25108,9 +26281,12 @@
         </is>
       </c>
       <c r="D391" s="4">
+        <v>7</v>
+      </c>
+      <c r="E391" s="4">
         <v>1</v>
       </c>
-      <c r="E391" s="6" t="inlineStr">
+      <c r="F391" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25171,9 +26347,12 @@
         </is>
       </c>
       <c r="D392" s="4">
+        <v>7</v>
+      </c>
+      <c r="E392" s="4">
         <v>2</v>
       </c>
-      <c r="E392" s="6" t="inlineStr">
+      <c r="F392" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25234,9 +26413,12 @@
         </is>
       </c>
       <c r="D393" s="4">
+        <v>7</v>
+      </c>
+      <c r="E393" s="4">
         <v>3</v>
       </c>
-      <c r="E393" s="6" t="inlineStr">
+      <c r="F393" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25297,9 +26479,12 @@
         </is>
       </c>
       <c r="D394" s="4">
+        <v>7</v>
+      </c>
+      <c r="E394" s="4">
         <v>4</v>
       </c>
-      <c r="E394" s="6" t="inlineStr">
+      <c r="F394" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25360,9 +26545,12 @@
         </is>
       </c>
       <c r="D395" s="4">
+        <v>7</v>
+      </c>
+      <c r="E395" s="4">
         <v>5</v>
       </c>
-      <c r="E395" s="6" t="inlineStr">
+      <c r="F395" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25423,9 +26611,12 @@
         </is>
       </c>
       <c r="D396" s="4">
+        <v>7</v>
+      </c>
+      <c r="E396" s="4">
         <v>6</v>
       </c>
-      <c r="E396" s="6" t="inlineStr">
+      <c r="F396" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25488,7 +26679,10 @@
       <c r="D397" s="4">
         <v>7</v>
       </c>
-      <c r="E397" s="6" t="inlineStr">
+      <c r="E397" s="4">
+        <v>7</v>
+      </c>
+      <c r="F397" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25549,9 +26743,12 @@
         </is>
       </c>
       <c r="D398" s="4">
+        <v>3</v>
+      </c>
+      <c r="E398" s="4">
         <v>1</v>
       </c>
-      <c r="E398" s="6" t="inlineStr">
+      <c r="F398" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25620,9 +26817,12 @@
         </is>
       </c>
       <c r="D399" s="4">
+        <v>3</v>
+      </c>
+      <c r="E399" s="4">
         <v>2</v>
       </c>
-      <c r="E399" s="6" t="inlineStr">
+      <c r="F399" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25693,7 +26893,10 @@
       <c r="D400" s="4">
         <v>3</v>
       </c>
-      <c r="E400" s="6" t="inlineStr">
+      <c r="E400" s="4">
+        <v>3</v>
+      </c>
+      <c r="F400" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25762,9 +26965,12 @@
         </is>
       </c>
       <c r="D401" s="4">
+        <v>2</v>
+      </c>
+      <c r="E401" s="4">
         <v>1</v>
       </c>
-      <c r="E401" s="6" t="inlineStr">
+      <c r="F401" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25827,7 +27033,10 @@
       <c r="D402" s="4">
         <v>2</v>
       </c>
-      <c r="E402" s="6" t="inlineStr">
+      <c r="E402" s="4">
+        <v>2</v>
+      </c>
+      <c r="F402" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25890,7 +27099,10 @@
       <c r="D403" s="4">
         <v>1</v>
       </c>
-      <c r="E403" s="6" t="inlineStr">
+      <c r="E403" s="4">
+        <v>1</v>
+      </c>
+      <c r="F403" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25968,7 +27180,10 @@
       <c r="D404" s="4">
         <v>1</v>
       </c>
-      <c r="E404" s="6" t="inlineStr">
+      <c r="E404" s="4">
+        <v>1</v>
+      </c>
+      <c r="F404" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26038,9 +27253,12 @@
         </is>
       </c>
       <c r="D405" s="4">
+        <v>2</v>
+      </c>
+      <c r="E405" s="4">
         <v>1</v>
       </c>
-      <c r="E405" s="6" t="inlineStr">
+      <c r="F405" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26103,7 +27321,10 @@
       <c r="D406" s="4">
         <v>2</v>
       </c>
-      <c r="E406" s="6" t="inlineStr">
+      <c r="E406" s="4">
+        <v>2</v>
+      </c>
+      <c r="F406" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26164,9 +27385,12 @@
         </is>
       </c>
       <c r="D407" s="4">
+        <v>6</v>
+      </c>
+      <c r="E407" s="4">
         <v>1</v>
       </c>
-      <c r="E407" s="6" t="inlineStr">
+      <c r="F407" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26236,9 +27460,12 @@
         </is>
       </c>
       <c r="D408" s="4">
+        <v>6</v>
+      </c>
+      <c r="E408" s="4">
         <v>2</v>
       </c>
-      <c r="E408" s="6" t="inlineStr">
+      <c r="F408" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26308,9 +27535,12 @@
         </is>
       </c>
       <c r="D409" s="4">
+        <v>6</v>
+      </c>
+      <c r="E409" s="4">
         <v>3</v>
       </c>
-      <c r="E409" s="6" t="inlineStr">
+      <c r="F409" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26380,9 +27610,12 @@
         </is>
       </c>
       <c r="D410" s="4">
+        <v>6</v>
+      </c>
+      <c r="E410" s="4">
         <v>4</v>
       </c>
-      <c r="E410" s="6" t="inlineStr">
+      <c r="F410" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26452,9 +27685,12 @@
         </is>
       </c>
       <c r="D411" s="4">
+        <v>6</v>
+      </c>
+      <c r="E411" s="4">
         <v>5</v>
       </c>
-      <c r="E411" s="6" t="inlineStr">
+      <c r="F411" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26526,7 +27762,10 @@
       <c r="D412" s="4">
         <v>6</v>
       </c>
-      <c r="E412" s="6" t="inlineStr">
+      <c r="E412" s="4">
+        <v>6</v>
+      </c>
+      <c r="F412" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26596,9 +27835,12 @@
         </is>
       </c>
       <c r="D413" s="4">
+        <v>10</v>
+      </c>
+      <c r="E413" s="4">
         <v>1</v>
       </c>
-      <c r="E413" s="6" t="inlineStr">
+      <c r="F413" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26668,9 +27910,12 @@
         </is>
       </c>
       <c r="D414" s="4">
+        <v>10</v>
+      </c>
+      <c r="E414" s="4">
         <v>2</v>
       </c>
-      <c r="E414" s="6" t="inlineStr">
+      <c r="F414" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26740,9 +27985,12 @@
         </is>
       </c>
       <c r="D415" s="4">
+        <v>10</v>
+      </c>
+      <c r="E415" s="4">
         <v>3</v>
       </c>
-      <c r="E415" s="6" t="inlineStr">
+      <c r="F415" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26812,9 +28060,12 @@
         </is>
       </c>
       <c r="D416" s="4">
+        <v>10</v>
+      </c>
+      <c r="E416" s="4">
         <v>4</v>
       </c>
-      <c r="E416" s="6" t="inlineStr">
+      <c r="F416" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26884,9 +28135,12 @@
         </is>
       </c>
       <c r="D417" s="4">
+        <v>10</v>
+      </c>
+      <c r="E417" s="4">
         <v>5</v>
       </c>
-      <c r="E417" s="6" t="inlineStr">
+      <c r="F417" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26956,9 +28210,12 @@
         </is>
       </c>
       <c r="D418" s="4">
+        <v>10</v>
+      </c>
+      <c r="E418" s="4">
         <v>6</v>
       </c>
-      <c r="E418" s="6" t="inlineStr">
+      <c r="F418" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27028,9 +28285,12 @@
         </is>
       </c>
       <c r="D419" s="4">
+        <v>10</v>
+      </c>
+      <c r="E419" s="4">
         <v>7</v>
       </c>
-      <c r="E419" s="6" t="inlineStr">
+      <c r="F419" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27100,9 +28360,12 @@
         </is>
       </c>
       <c r="D420" s="4">
+        <v>10</v>
+      </c>
+      <c r="E420" s="4">
         <v>8</v>
       </c>
-      <c r="E420" s="6" t="inlineStr">
+      <c r="F420" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27172,9 +28435,12 @@
         </is>
       </c>
       <c r="D421" s="4">
+        <v>10</v>
+      </c>
+      <c r="E421" s="4">
         <v>9</v>
       </c>
-      <c r="E421" s="6" t="inlineStr">
+      <c r="F421" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27246,7 +28512,10 @@
       <c r="D422" s="4">
         <v>10</v>
       </c>
-      <c r="E422" s="6" t="inlineStr">
+      <c r="E422" s="4">
+        <v>10</v>
+      </c>
+      <c r="F422" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27318,7 +28587,10 @@
       <c r="D423" s="4">
         <v>1</v>
       </c>
-      <c r="E423" s="6" t="inlineStr">
+      <c r="E423" s="4">
+        <v>1</v>
+      </c>
+      <c r="F423" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27374,7 +28646,10 @@
       <c r="D424" s="4">
         <v>1</v>
       </c>
-      <c r="E424" s="6" t="inlineStr">
+      <c r="E424" s="4">
+        <v>1</v>
+      </c>
+      <c r="F424" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27428,9 +28703,12 @@
         </is>
       </c>
       <c r="D425" s="4">
+        <v>4</v>
+      </c>
+      <c r="E425" s="4">
         <v>1</v>
       </c>
-      <c r="E425" s="6" t="inlineStr">
+      <c r="F425" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27484,9 +28762,12 @@
         </is>
       </c>
       <c r="D426" s="4">
+        <v>4</v>
+      </c>
+      <c r="E426" s="4">
         <v>2</v>
       </c>
-      <c r="E426" s="6" t="inlineStr">
+      <c r="F426" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27540,9 +28821,12 @@
         </is>
       </c>
       <c r="D427" s="4">
+        <v>4</v>
+      </c>
+      <c r="E427" s="4">
         <v>3</v>
       </c>
-      <c r="E427" s="6" t="inlineStr">
+      <c r="F427" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27598,7 +28882,10 @@
       <c r="D428" s="4">
         <v>4</v>
       </c>
-      <c r="E428" s="6" t="inlineStr">
+      <c r="E428" s="4">
+        <v>4</v>
+      </c>
+      <c r="F428" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27654,7 +28941,10 @@
       <c r="D429" s="4">
         <v>1</v>
       </c>
-      <c r="E429" s="6" t="inlineStr">
+      <c r="E429" s="4">
+        <v>1</v>
+      </c>
+      <c r="F429" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27726,7 +29016,10 @@
       <c r="D430" s="4">
         <v>1</v>
       </c>
-      <c r="E430" s="6" t="inlineStr">
+      <c r="E430" s="4">
+        <v>1</v>
+      </c>
+      <c r="F430" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27789,7 +29082,10 @@
       <c r="D431" s="4">
         <v>1</v>
       </c>
-      <c r="E431" s="6" t="inlineStr">
+      <c r="E431" s="4">
+        <v>1</v>
+      </c>
+      <c r="F431" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27860,7 +29156,10 @@
       <c r="D432" s="4">
         <v>1</v>
       </c>
-      <c r="E432" s="6" t="inlineStr">
+      <c r="E432" s="4">
+        <v>1</v>
+      </c>
+      <c r="F432" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27931,7 +29230,10 @@
       <c r="D433" s="4">
         <v>1</v>
       </c>
-      <c r="E433" s="6" t="inlineStr">
+      <c r="E433" s="4">
+        <v>1</v>
+      </c>
+      <c r="F433" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28077,7 +29379,10 @@
       <c r="D434" s="4">
         <v>1</v>
       </c>
-      <c r="E434" s="6" t="inlineStr">
+      <c r="E434" s="4">
+        <v>1</v>
+      </c>
+      <c r="F434" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28140,7 +29445,10 @@
       <c r="D435" s="4">
         <v>1</v>
       </c>
-      <c r="E435" s="6" t="inlineStr">
+      <c r="E435" s="4">
+        <v>1</v>
+      </c>
+      <c r="F435" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28233,7 +29541,10 @@
       <c r="D436" s="4">
         <v>1</v>
       </c>
-      <c r="E436" s="6" t="inlineStr">
+      <c r="E436" s="4">
+        <v>1</v>
+      </c>
+      <c r="F436" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28319,7 +29630,10 @@
       <c r="D437" s="4">
         <v>1</v>
       </c>
-      <c r="E437" s="6" t="inlineStr">
+      <c r="E437" s="4">
+        <v>1</v>
+      </c>
+      <c r="F437" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28389,9 +29703,12 @@
         </is>
       </c>
       <c r="D438" s="4">
+        <v>11</v>
+      </c>
+      <c r="E438" s="4">
         <v>1</v>
       </c>
-      <c r="E438" s="6" t="inlineStr">
+      <c r="F438" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28452,9 +29769,12 @@
         </is>
       </c>
       <c r="D439" s="4">
+        <v>11</v>
+      </c>
+      <c r="E439" s="4">
         <v>2</v>
       </c>
-      <c r="E439" s="6" t="inlineStr">
+      <c r="F439" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28515,9 +29835,12 @@
         </is>
       </c>
       <c r="D440" s="4">
+        <v>11</v>
+      </c>
+      <c r="E440" s="4">
         <v>3</v>
       </c>
-      <c r="E440" s="6" t="inlineStr">
+      <c r="F440" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28578,9 +29901,12 @@
         </is>
       </c>
       <c r="D441" s="4">
+        <v>11</v>
+      </c>
+      <c r="E441" s="4">
         <v>4</v>
       </c>
-      <c r="E441" s="6" t="inlineStr">
+      <c r="F441" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28641,9 +29967,12 @@
         </is>
       </c>
       <c r="D442" s="4">
+        <v>11</v>
+      </c>
+      <c r="E442" s="4">
         <v>5</v>
       </c>
-      <c r="E442" s="6" t="inlineStr">
+      <c r="F442" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28704,9 +30033,12 @@
         </is>
       </c>
       <c r="D443" s="4">
+        <v>11</v>
+      </c>
+      <c r="E443" s="4">
         <v>6</v>
       </c>
-      <c r="E443" s="6" t="inlineStr">
+      <c r="F443" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28767,9 +30099,12 @@
         </is>
       </c>
       <c r="D444" s="4">
+        <v>11</v>
+      </c>
+      <c r="E444" s="4">
         <v>7</v>
       </c>
-      <c r="E444" s="6" t="inlineStr">
+      <c r="F444" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28830,9 +30165,12 @@
         </is>
       </c>
       <c r="D445" s="4">
+        <v>11</v>
+      </c>
+      <c r="E445" s="4">
         <v>8</v>
       </c>
-      <c r="E445" s="6" t="inlineStr">
+      <c r="F445" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28893,9 +30231,12 @@
         </is>
       </c>
       <c r="D446" s="4">
+        <v>11</v>
+      </c>
+      <c r="E446" s="4">
         <v>9</v>
       </c>
-      <c r="E446" s="6" t="inlineStr">
+      <c r="F446" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28956,9 +30297,12 @@
         </is>
       </c>
       <c r="D447" s="4">
+        <v>11</v>
+      </c>
+      <c r="E447" s="4">
         <v>10</v>
       </c>
-      <c r="E447" s="6" t="inlineStr">
+      <c r="F447" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29021,7 +30365,10 @@
       <c r="D448" s="4">
         <v>11</v>
       </c>
-      <c r="E448" s="6" t="inlineStr">
+      <c r="E448" s="4">
+        <v>11</v>
+      </c>
+      <c r="F448" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29084,7 +30431,10 @@
       <c r="D449" s="4">
         <v>1</v>
       </c>
-      <c r="E449" s="6" t="inlineStr">
+      <c r="E449" s="4">
+        <v>1</v>
+      </c>
+      <c r="F449" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29145,9 +30495,12 @@
         </is>
       </c>
       <c r="D450" s="4">
+        <v>9</v>
+      </c>
+      <c r="E450" s="4">
         <v>1</v>
       </c>
-      <c r="E450" s="6" t="inlineStr">
+      <c r="F450" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29217,9 +30570,12 @@
         </is>
       </c>
       <c r="D451" s="4">
+        <v>9</v>
+      </c>
+      <c r="E451" s="4">
         <v>2</v>
       </c>
-      <c r="E451" s="6" t="inlineStr">
+      <c r="F451" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29289,9 +30645,12 @@
         </is>
       </c>
       <c r="D452" s="4">
+        <v>9</v>
+      </c>
+      <c r="E452" s="4">
         <v>3</v>
       </c>
-      <c r="E452" s="6" t="inlineStr">
+      <c r="F452" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29361,9 +30720,12 @@
         </is>
       </c>
       <c r="D453" s="4">
+        <v>9</v>
+      </c>
+      <c r="E453" s="4">
         <v>4</v>
       </c>
-      <c r="E453" s="6" t="inlineStr">
+      <c r="F453" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29433,9 +30795,12 @@
         </is>
       </c>
       <c r="D454" s="4">
+        <v>9</v>
+      </c>
+      <c r="E454" s="4">
         <v>5</v>
       </c>
-      <c r="E454" s="6" t="inlineStr">
+      <c r="F454" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29505,9 +30870,12 @@
         </is>
       </c>
       <c r="D455" s="4">
+        <v>9</v>
+      </c>
+      <c r="E455" s="4">
         <v>6</v>
       </c>
-      <c r="E455" s="6" t="inlineStr">
+      <c r="F455" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29577,9 +30945,12 @@
         </is>
       </c>
       <c r="D456" s="4">
+        <v>9</v>
+      </c>
+      <c r="E456" s="4">
         <v>7</v>
       </c>
-      <c r="E456" s="6" t="inlineStr">
+      <c r="F456" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29649,9 +31020,12 @@
         </is>
       </c>
       <c r="D457" s="4">
+        <v>9</v>
+      </c>
+      <c r="E457" s="4">
         <v>8</v>
       </c>
-      <c r="E457" s="6" t="inlineStr">
+      <c r="F457" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29723,7 +31097,10 @@
       <c r="D458" s="4">
         <v>9</v>
       </c>
-      <c r="E458" s="6" t="inlineStr">
+      <c r="E458" s="4">
+        <v>9</v>
+      </c>
+      <c r="F458" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29793,9 +31170,12 @@
         </is>
       </c>
       <c r="D459" s="4">
+        <v>4</v>
+      </c>
+      <c r="E459" s="4">
         <v>1</v>
       </c>
-      <c r="E459" s="6" t="inlineStr">
+      <c r="F459" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29865,9 +31245,12 @@
         </is>
       </c>
       <c r="D460" s="4">
+        <v>4</v>
+      </c>
+      <c r="E460" s="4">
         <v>2</v>
       </c>
-      <c r="E460" s="6" t="inlineStr">
+      <c r="F460" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29937,9 +31320,12 @@
         </is>
       </c>
       <c r="D461" s="4">
+        <v>4</v>
+      </c>
+      <c r="E461" s="4">
         <v>3</v>
       </c>
-      <c r="E461" s="6" t="inlineStr">
+      <c r="F461" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30011,7 +31397,10 @@
       <c r="D462" s="4">
         <v>4</v>
       </c>
-      <c r="E462" s="6" t="inlineStr">
+      <c r="E462" s="4">
+        <v>4</v>
+      </c>
+      <c r="F462" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30081,9 +31470,12 @@
         </is>
       </c>
       <c r="D463" s="4">
+        <v>11</v>
+      </c>
+      <c r="E463" s="4">
         <v>1</v>
       </c>
-      <c r="E463" s="6" t="inlineStr">
+      <c r="F463" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30153,9 +31545,12 @@
         </is>
       </c>
       <c r="D464" s="4">
+        <v>11</v>
+      </c>
+      <c r="E464" s="4">
         <v>2</v>
       </c>
-      <c r="E464" s="6" t="inlineStr">
+      <c r="F464" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30225,9 +31620,12 @@
         </is>
       </c>
       <c r="D465" s="4">
+        <v>11</v>
+      </c>
+      <c r="E465" s="4">
         <v>3</v>
       </c>
-      <c r="E465" s="6" t="inlineStr">
+      <c r="F465" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30297,9 +31695,12 @@
         </is>
       </c>
       <c r="D466" s="4">
+        <v>11</v>
+      </c>
+      <c r="E466" s="4">
         <v>4</v>
       </c>
-      <c r="E466" s="6" t="inlineStr">
+      <c r="F466" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30369,9 +31770,12 @@
         </is>
       </c>
       <c r="D467" s="4">
+        <v>11</v>
+      </c>
+      <c r="E467" s="4">
         <v>5</v>
       </c>
-      <c r="E467" s="6" t="inlineStr">
+      <c r="F467" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30441,9 +31845,12 @@
         </is>
       </c>
       <c r="D468" s="4">
+        <v>11</v>
+      </c>
+      <c r="E468" s="4">
         <v>6</v>
       </c>
-      <c r="E468" s="6" t="inlineStr">
+      <c r="F468" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30513,9 +31920,12 @@
         </is>
       </c>
       <c r="D469" s="4">
+        <v>11</v>
+      </c>
+      <c r="E469" s="4">
         <v>7</v>
       </c>
-      <c r="E469" s="6" t="inlineStr">
+      <c r="F469" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30585,9 +31995,12 @@
         </is>
       </c>
       <c r="D470" s="4">
+        <v>11</v>
+      </c>
+      <c r="E470" s="4">
         <v>8</v>
       </c>
-      <c r="E470" s="6" t="inlineStr">
+      <c r="F470" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30657,9 +32070,12 @@
         </is>
       </c>
       <c r="D471" s="4">
+        <v>11</v>
+      </c>
+      <c r="E471" s="4">
         <v>9</v>
       </c>
-      <c r="E471" s="6" t="inlineStr">
+      <c r="F471" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30729,9 +32145,12 @@
         </is>
       </c>
       <c r="D472" s="4">
+        <v>11</v>
+      </c>
+      <c r="E472" s="4">
         <v>10</v>
       </c>
-      <c r="E472" s="6" t="inlineStr">
+      <c r="F472" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30803,7 +32222,10 @@
       <c r="D473" s="4">
         <v>11</v>
       </c>
-      <c r="E473" s="6" t="inlineStr">
+      <c r="E473" s="4">
+        <v>11</v>
+      </c>
+      <c r="F473" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30873,9 +32295,12 @@
         </is>
       </c>
       <c r="D474" s="4">
+        <v>9</v>
+      </c>
+      <c r="E474" s="4">
         <v>1</v>
       </c>
-      <c r="E474" s="6" t="inlineStr">
+      <c r="F474" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30945,9 +32370,12 @@
         </is>
       </c>
       <c r="D475" s="4">
+        <v>9</v>
+      </c>
+      <c r="E475" s="4">
         <v>2</v>
       </c>
-      <c r="E475" s="6" t="inlineStr">
+      <c r="F475" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31017,9 +32445,12 @@
         </is>
       </c>
       <c r="D476" s="4">
+        <v>9</v>
+      </c>
+      <c r="E476" s="4">
         <v>3</v>
       </c>
-      <c r="E476" s="6" t="inlineStr">
+      <c r="F476" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31089,9 +32520,12 @@
         </is>
       </c>
       <c r="D477" s="4">
+        <v>9</v>
+      </c>
+      <c r="E477" s="4">
         <v>4</v>
       </c>
-      <c r="E477" s="6" t="inlineStr">
+      <c r="F477" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31161,9 +32595,12 @@
         </is>
       </c>
       <c r="D478" s="4">
+        <v>9</v>
+      </c>
+      <c r="E478" s="4">
         <v>5</v>
       </c>
-      <c r="E478" s="6" t="inlineStr">
+      <c r="F478" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31233,9 +32670,12 @@
         </is>
       </c>
       <c r="D479" s="4">
+        <v>9</v>
+      </c>
+      <c r="E479" s="4">
         <v>6</v>
       </c>
-      <c r="E479" s="6" t="inlineStr">
+      <c r="F479" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31305,9 +32745,12 @@
         </is>
       </c>
       <c r="D480" s="4">
+        <v>9</v>
+      </c>
+      <c r="E480" s="4">
         <v>7</v>
       </c>
-      <c r="E480" s="6" t="inlineStr">
+      <c r="F480" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31377,9 +32820,12 @@
         </is>
       </c>
       <c r="D481" s="4">
+        <v>9</v>
+      </c>
+      <c r="E481" s="4">
         <v>8</v>
       </c>
-      <c r="E481" s="6" t="inlineStr">
+      <c r="F481" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31451,7 +32897,10 @@
       <c r="D482" s="4">
         <v>9</v>
       </c>
-      <c r="E482" s="6" t="inlineStr">
+      <c r="E482" s="4">
+        <v>9</v>
+      </c>
+      <c r="F482" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31521,9 +32970,12 @@
         </is>
       </c>
       <c r="D483" s="4">
+        <v>6</v>
+      </c>
+      <c r="E483" s="4">
         <v>1</v>
       </c>
-      <c r="E483" s="6" t="inlineStr">
+      <c r="F483" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31593,9 +33045,12 @@
         </is>
       </c>
       <c r="D484" s="4">
+        <v>6</v>
+      </c>
+      <c r="E484" s="4">
         <v>2</v>
       </c>
-      <c r="E484" s="6" t="inlineStr">
+      <c r="F484" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31665,9 +33120,12 @@
         </is>
       </c>
       <c r="D485" s="4">
+        <v>6</v>
+      </c>
+      <c r="E485" s="4">
         <v>3</v>
       </c>
-      <c r="E485" s="6" t="inlineStr">
+      <c r="F485" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31737,9 +33195,12 @@
         </is>
       </c>
       <c r="D486" s="4">
+        <v>6</v>
+      </c>
+      <c r="E486" s="4">
         <v>4</v>
       </c>
-      <c r="E486" s="6" t="inlineStr">
+      <c r="F486" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31809,9 +33270,12 @@
         </is>
       </c>
       <c r="D487" s="4">
+        <v>6</v>
+      </c>
+      <c r="E487" s="4">
         <v>5</v>
       </c>
-      <c r="E487" s="6" t="inlineStr">
+      <c r="F487" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31883,7 +33347,10 @@
       <c r="D488" s="4">
         <v>6</v>
       </c>
-      <c r="E488" s="6" t="inlineStr">
+      <c r="E488" s="4">
+        <v>6</v>
+      </c>
+      <c r="F488" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31953,9 +33420,12 @@
         </is>
       </c>
       <c r="D489" s="4">
+        <v>10</v>
+      </c>
+      <c r="E489" s="4">
         <v>1</v>
       </c>
-      <c r="E489" s="6" t="inlineStr">
+      <c r="F489" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32025,9 +33495,12 @@
         </is>
       </c>
       <c r="D490" s="4">
+        <v>10</v>
+      </c>
+      <c r="E490" s="4">
         <v>2</v>
       </c>
-      <c r="E490" s="6" t="inlineStr">
+      <c r="F490" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32097,9 +33570,12 @@
         </is>
       </c>
       <c r="D491" s="4">
+        <v>10</v>
+      </c>
+      <c r="E491" s="4">
         <v>3</v>
       </c>
-      <c r="E491" s="6" t="inlineStr">
+      <c r="F491" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32169,9 +33645,12 @@
         </is>
       </c>
       <c r="D492" s="4">
+        <v>10</v>
+      </c>
+      <c r="E492" s="4">
         <v>4</v>
       </c>
-      <c r="E492" s="6" t="inlineStr">
+      <c r="F492" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32241,9 +33720,12 @@
         </is>
       </c>
       <c r="D493" s="4">
+        <v>10</v>
+      </c>
+      <c r="E493" s="4">
         <v>5</v>
       </c>
-      <c r="E493" s="6" t="inlineStr">
+      <c r="F493" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32313,9 +33795,12 @@
         </is>
       </c>
       <c r="D494" s="4">
+        <v>10</v>
+      </c>
+      <c r="E494" s="4">
         <v>6</v>
       </c>
-      <c r="E494" s="6" t="inlineStr">
+      <c r="F494" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32385,9 +33870,12 @@
         </is>
       </c>
       <c r="D495" s="4">
+        <v>10</v>
+      </c>
+      <c r="E495" s="4">
         <v>7</v>
       </c>
-      <c r="E495" s="6" t="inlineStr">
+      <c r="F495" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32457,9 +33945,12 @@
         </is>
       </c>
       <c r="D496" s="4">
+        <v>10</v>
+      </c>
+      <c r="E496" s="4">
         <v>8</v>
       </c>
-      <c r="E496" s="6" t="inlineStr">
+      <c r="F496" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32529,9 +34020,12 @@
         </is>
       </c>
       <c r="D497" s="4">
+        <v>10</v>
+      </c>
+      <c r="E497" s="4">
         <v>9</v>
       </c>
-      <c r="E497" s="6" t="inlineStr">
+      <c r="F497" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32603,7 +34097,10 @@
       <c r="D498" s="4">
         <v>10</v>
       </c>
-      <c r="E498" s="6" t="inlineStr">
+      <c r="E498" s="4">
+        <v>10</v>
+      </c>
+      <c r="F498" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32673,9 +34170,12 @@
         </is>
       </c>
       <c r="D499" s="4">
+        <v>6</v>
+      </c>
+      <c r="E499" s="4">
         <v>1</v>
       </c>
-      <c r="E499" s="6" t="inlineStr">
+      <c r="F499" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32745,9 +34245,12 @@
         </is>
       </c>
       <c r="D500" s="4">
+        <v>6</v>
+      </c>
+      <c r="E500" s="4">
         <v>2</v>
       </c>
-      <c r="E500" s="6" t="inlineStr">
+      <c r="F500" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32817,9 +34320,12 @@
         </is>
       </c>
       <c r="D501" s="4">
+        <v>6</v>
+      </c>
+      <c r="E501" s="4">
         <v>3</v>
       </c>
-      <c r="E501" s="6" t="inlineStr">
+      <c r="F501" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32889,9 +34395,12 @@
         </is>
       </c>
       <c r="D502" s="4">
+        <v>6</v>
+      </c>
+      <c r="E502" s="4">
         <v>4</v>
       </c>
-      <c r="E502" s="6" t="inlineStr">
+      <c r="F502" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32961,9 +34470,12 @@
         </is>
       </c>
       <c r="D503" s="4">
+        <v>6</v>
+      </c>
+      <c r="E503" s="4">
         <v>5</v>
       </c>
-      <c r="E503" s="6" t="inlineStr">
+      <c r="F503" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33035,7 +34547,10 @@
       <c r="D504" s="4">
         <v>6</v>
       </c>
-      <c r="E504" s="6" t="inlineStr">
+      <c r="E504" s="4">
+        <v>6</v>
+      </c>
+      <c r="F504" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33105,9 +34620,12 @@
         </is>
       </c>
       <c r="D505" s="4">
+        <v>12</v>
+      </c>
+      <c r="E505" s="4">
         <v>1</v>
       </c>
-      <c r="E505" s="6" t="inlineStr">
+      <c r="F505" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33177,9 +34695,12 @@
         </is>
       </c>
       <c r="D506" s="4">
+        <v>12</v>
+      </c>
+      <c r="E506" s="4">
         <v>2</v>
       </c>
-      <c r="E506" s="6" t="inlineStr">
+      <c r="F506" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33249,9 +34770,12 @@
         </is>
       </c>
       <c r="D507" s="4">
+        <v>12</v>
+      </c>
+      <c r="E507" s="4">
         <v>3</v>
       </c>
-      <c r="E507" s="6" t="inlineStr">
+      <c r="F507" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33321,9 +34845,12 @@
         </is>
       </c>
       <c r="D508" s="4">
+        <v>12</v>
+      </c>
+      <c r="E508" s="4">
         <v>4</v>
       </c>
-      <c r="E508" s="6" t="inlineStr">
+      <c r="F508" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33393,9 +34920,12 @@
         </is>
       </c>
       <c r="D509" s="4">
+        <v>12</v>
+      </c>
+      <c r="E509" s="4">
         <v>5</v>
       </c>
-      <c r="E509" s="6" t="inlineStr">
+      <c r="F509" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33465,9 +34995,12 @@
         </is>
       </c>
       <c r="D510" s="4">
+        <v>12</v>
+      </c>
+      <c r="E510" s="4">
         <v>6</v>
       </c>
-      <c r="E510" s="6" t="inlineStr">
+      <c r="F510" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33537,9 +35070,12 @@
         </is>
       </c>
       <c r="D511" s="4">
+        <v>12</v>
+      </c>
+      <c r="E511" s="4">
         <v>7</v>
       </c>
-      <c r="E511" s="6" t="inlineStr">
+      <c r="F511" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33609,9 +35145,12 @@
         </is>
       </c>
       <c r="D512" s="4">
+        <v>12</v>
+      </c>
+      <c r="E512" s="4">
         <v>8</v>
       </c>
-      <c r="E512" s="6" t="inlineStr">
+      <c r="F512" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33681,9 +35220,12 @@
         </is>
       </c>
       <c r="D513" s="4">
+        <v>12</v>
+      </c>
+      <c r="E513" s="4">
         <v>9</v>
       </c>
-      <c r="E513" s="6" t="inlineStr">
+      <c r="F513" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33753,9 +35295,12 @@
         </is>
       </c>
       <c r="D514" s="4">
+        <v>12</v>
+      </c>
+      <c r="E514" s="4">
         <v>10</v>
       </c>
-      <c r="E514" s="6" t="inlineStr">
+      <c r="F514" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33825,9 +35370,12 @@
         </is>
       </c>
       <c r="D515" s="4">
+        <v>12</v>
+      </c>
+      <c r="E515" s="4">
         <v>11</v>
       </c>
-      <c r="E515" s="6" t="inlineStr">
+      <c r="F515" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33899,7 +35447,10 @@
       <c r="D516" s="4">
         <v>12</v>
       </c>
-      <c r="E516" s="6" t="inlineStr">
+      <c r="E516" s="4">
+        <v>12</v>
+      </c>
+      <c r="F516" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33969,9 +35520,12 @@
         </is>
       </c>
       <c r="D517" s="4">
+        <v>10</v>
+      </c>
+      <c r="E517" s="4">
         <v>1</v>
       </c>
-      <c r="E517" s="6" t="inlineStr">
+      <c r="F517" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34041,9 +35595,12 @@
         </is>
       </c>
       <c r="D518" s="4">
+        <v>10</v>
+      </c>
+      <c r="E518" s="4">
         <v>2</v>
       </c>
-      <c r="E518" s="6" t="inlineStr">
+      <c r="F518" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34113,9 +35670,12 @@
         </is>
       </c>
       <c r="D519" s="4">
+        <v>10</v>
+      </c>
+      <c r="E519" s="4">
         <v>3</v>
       </c>
-      <c r="E519" s="6" t="inlineStr">
+      <c r="F519" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34185,9 +35745,12 @@
         </is>
       </c>
       <c r="D520" s="4">
+        <v>10</v>
+      </c>
+      <c r="E520" s="4">
         <v>4</v>
       </c>
-      <c r="E520" s="6" t="inlineStr">
+      <c r="F520" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34257,9 +35820,12 @@
         </is>
       </c>
       <c r="D521" s="4">
+        <v>10</v>
+      </c>
+      <c r="E521" s="4">
         <v>5</v>
       </c>
-      <c r="E521" s="6" t="inlineStr">
+      <c r="F521" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34329,9 +35895,12 @@
         </is>
       </c>
       <c r="D522" s="4">
+        <v>10</v>
+      </c>
+      <c r="E522" s="4">
         <v>6</v>
       </c>
-      <c r="E522" s="6" t="inlineStr">
+      <c r="F522" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34401,9 +35970,12 @@
         </is>
       </c>
       <c r="D523" s="4">
+        <v>10</v>
+      </c>
+      <c r="E523" s="4">
         <v>7</v>
       </c>
-      <c r="E523" s="6" t="inlineStr">
+      <c r="F523" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34473,9 +36045,12 @@
         </is>
       </c>
       <c r="D524" s="4">
+        <v>10</v>
+      </c>
+      <c r="E524" s="4">
         <v>8</v>
       </c>
-      <c r="E524" s="6" t="inlineStr">
+      <c r="F524" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34545,9 +36120,12 @@
         </is>
       </c>
       <c r="D525" s="4">
+        <v>10</v>
+      </c>
+      <c r="E525" s="4">
         <v>9</v>
       </c>
-      <c r="E525" s="6" t="inlineStr">
+      <c r="F525" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34619,7 +36197,10 @@
       <c r="D526" s="4">
         <v>10</v>
       </c>
-      <c r="E526" s="6" t="inlineStr">
+      <c r="E526" s="4">
+        <v>10</v>
+      </c>
+      <c r="F526" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34689,9 +36270,12 @@
         </is>
       </c>
       <c r="D527" s="4">
+        <v>6</v>
+      </c>
+      <c r="E527" s="4">
         <v>1</v>
       </c>
-      <c r="E527" s="6" t="inlineStr">
+      <c r="F527" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34761,9 +36345,12 @@
         </is>
       </c>
       <c r="D528" s="4">
+        <v>6</v>
+      </c>
+      <c r="E528" s="4">
         <v>2</v>
       </c>
-      <c r="E528" s="6" t="inlineStr">
+      <c r="F528" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34833,9 +36420,12 @@
         </is>
       </c>
       <c r="D529" s="4">
+        <v>6</v>
+      </c>
+      <c r="E529" s="4">
         <v>3</v>
       </c>
-      <c r="E529" s="6" t="inlineStr">
+      <c r="F529" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34905,9 +36495,12 @@
         </is>
       </c>
       <c r="D530" s="4">
+        <v>6</v>
+      </c>
+      <c r="E530" s="4">
         <v>4</v>
       </c>
-      <c r="E530" s="6" t="inlineStr">
+      <c r="F530" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34977,9 +36570,12 @@
         </is>
       </c>
       <c r="D531" s="4">
+        <v>6</v>
+      </c>
+      <c r="E531" s="4">
         <v>5</v>
       </c>
-      <c r="E531" s="6" t="inlineStr">
+      <c r="F531" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35051,7 +36647,10 @@
       <c r="D532" s="4">
         <v>6</v>
       </c>
-      <c r="E532" s="6" t="inlineStr">
+      <c r="E532" s="4">
+        <v>6</v>
+      </c>
+      <c r="F532" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35121,9 +36720,12 @@
         </is>
       </c>
       <c r="D533" s="4">
+        <v>5</v>
+      </c>
+      <c r="E533" s="4">
         <v>1</v>
       </c>
-      <c r="E533" s="6" t="inlineStr">
+      <c r="F533" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35193,9 +36795,12 @@
         </is>
       </c>
       <c r="D534" s="4">
+        <v>5</v>
+      </c>
+      <c r="E534" s="4">
         <v>2</v>
       </c>
-      <c r="E534" s="6" t="inlineStr">
+      <c r="F534" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35265,9 +36870,12 @@
         </is>
       </c>
       <c r="D535" s="4">
+        <v>5</v>
+      </c>
+      <c r="E535" s="4">
         <v>3</v>
       </c>
-      <c r="E535" s="6" t="inlineStr">
+      <c r="F535" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35337,9 +36945,12 @@
         </is>
       </c>
       <c r="D536" s="4">
+        <v>5</v>
+      </c>
+      <c r="E536" s="4">
         <v>4</v>
       </c>
-      <c r="E536" s="6" t="inlineStr">
+      <c r="F536" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35411,7 +37022,10 @@
       <c r="D537" s="4">
         <v>5</v>
       </c>
-      <c r="E537" s="6" t="inlineStr">
+      <c r="E537" s="4">
+        <v>5</v>
+      </c>
+      <c r="F537" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35481,9 +37095,12 @@
         </is>
       </c>
       <c r="D538" s="4">
+        <v>17</v>
+      </c>
+      <c r="E538" s="4">
         <v>1</v>
       </c>
-      <c r="E538" s="6" t="inlineStr">
+      <c r="F538" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35553,9 +37170,12 @@
         </is>
       </c>
       <c r="D539" s="4">
+        <v>17</v>
+      </c>
+      <c r="E539" s="4">
         <v>2</v>
       </c>
-      <c r="E539" s="6" t="inlineStr">
+      <c r="F539" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35625,9 +37245,12 @@
         </is>
       </c>
       <c r="D540" s="4">
+        <v>17</v>
+      </c>
+      <c r="E540" s="4">
         <v>3</v>
       </c>
-      <c r="E540" s="6" t="inlineStr">
+      <c r="F540" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35697,9 +37320,12 @@
         </is>
       </c>
       <c r="D541" s="4">
+        <v>17</v>
+      </c>
+      <c r="E541" s="4">
         <v>4</v>
       </c>
-      <c r="E541" s="6" t="inlineStr">
+      <c r="F541" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35769,9 +37395,12 @@
         </is>
       </c>
       <c r="D542" s="4">
+        <v>17</v>
+      </c>
+      <c r="E542" s="4">
         <v>5</v>
       </c>
-      <c r="E542" s="6" t="inlineStr">
+      <c r="F542" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35841,9 +37470,12 @@
         </is>
       </c>
       <c r="D543" s="4">
+        <v>17</v>
+      </c>
+      <c r="E543" s="4">
         <v>6</v>
       </c>
-      <c r="E543" s="6" t="inlineStr">
+      <c r="F543" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35913,9 +37545,12 @@
         </is>
       </c>
       <c r="D544" s="4">
+        <v>17</v>
+      </c>
+      <c r="E544" s="4">
         <v>7</v>
       </c>
-      <c r="E544" s="6" t="inlineStr">
+      <c r="F544" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35985,9 +37620,12 @@
         </is>
       </c>
       <c r="D545" s="4">
+        <v>17</v>
+      </c>
+      <c r="E545" s="4">
         <v>8</v>
       </c>
-      <c r="E545" s="6" t="inlineStr">
+      <c r="F545" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36057,9 +37695,12 @@
         </is>
       </c>
       <c r="D546" s="4">
+        <v>17</v>
+      </c>
+      <c r="E546" s="4">
         <v>9</v>
       </c>
-      <c r="E546" s="6" t="inlineStr">
+      <c r="F546" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36129,9 +37770,12 @@
         </is>
       </c>
       <c r="D547" s="4">
+        <v>17</v>
+      </c>
+      <c r="E547" s="4">
         <v>10</v>
       </c>
-      <c r="E547" s="6" t="inlineStr">
+      <c r="F547" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36201,9 +37845,12 @@
         </is>
       </c>
       <c r="D548" s="4">
+        <v>17</v>
+      </c>
+      <c r="E548" s="4">
         <v>11</v>
       </c>
-      <c r="E548" s="6" t="inlineStr">
+      <c r="F548" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36273,9 +37920,12 @@
         </is>
       </c>
       <c r="D549" s="4">
+        <v>17</v>
+      </c>
+      <c r="E549" s="4">
         <v>12</v>
       </c>
-      <c r="E549" s="6" t="inlineStr">
+      <c r="F549" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36345,9 +37995,12 @@
         </is>
       </c>
       <c r="D550" s="4">
+        <v>17</v>
+      </c>
+      <c r="E550" s="4">
         <v>13</v>
       </c>
-      <c r="E550" s="6" t="inlineStr">
+      <c r="F550" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36417,9 +38070,12 @@
         </is>
       </c>
       <c r="D551" s="4">
+        <v>17</v>
+      </c>
+      <c r="E551" s="4">
         <v>14</v>
       </c>
-      <c r="E551" s="6" t="inlineStr">
+      <c r="F551" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36489,9 +38145,12 @@
         </is>
       </c>
       <c r="D552" s="4">
+        <v>17</v>
+      </c>
+      <c r="E552" s="4">
         <v>15</v>
       </c>
-      <c r="E552" s="6" t="inlineStr">
+      <c r="F552" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36561,9 +38220,12 @@
         </is>
       </c>
       <c r="D553" s="4">
+        <v>17</v>
+      </c>
+      <c r="E553" s="4">
         <v>16</v>
       </c>
-      <c r="E553" s="6" t="inlineStr">
+      <c r="F553" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36635,7 +38297,10 @@
       <c r="D554" s="4">
         <v>17</v>
       </c>
-      <c r="E554" s="6" t="inlineStr">
+      <c r="E554" s="4">
+        <v>17</v>
+      </c>
+      <c r="F554" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36705,9 +38370,12 @@
         </is>
       </c>
       <c r="D555" s="4">
+        <v>11</v>
+      </c>
+      <c r="E555" s="4">
         <v>1</v>
       </c>
-      <c r="E555" s="6" t="inlineStr">
+      <c r="F555" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36777,9 +38445,12 @@
         </is>
       </c>
       <c r="D556" s="4">
+        <v>11</v>
+      </c>
+      <c r="E556" s="4">
         <v>2</v>
       </c>
-      <c r="E556" s="6" t="inlineStr">
+      <c r="F556" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36849,9 +38520,12 @@
         </is>
       </c>
       <c r="D557" s="4">
+        <v>11</v>
+      </c>
+      <c r="E557" s="4">
         <v>3</v>
       </c>
-      <c r="E557" s="6" t="inlineStr">
+      <c r="F557" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36921,9 +38595,12 @@
         </is>
       </c>
       <c r="D558" s="4">
+        <v>11</v>
+      </c>
+      <c r="E558" s="4">
         <v>4</v>
       </c>
-      <c r="E558" s="6" t="inlineStr">
+      <c r="F558" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36993,9 +38670,12 @@
         </is>
       </c>
       <c r="D559" s="4">
+        <v>11</v>
+      </c>
+      <c r="E559" s="4">
         <v>5</v>
       </c>
-      <c r="E559" s="6" t="inlineStr">
+      <c r="F559" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37065,9 +38745,12 @@
         </is>
       </c>
       <c r="D560" s="4">
+        <v>11</v>
+      </c>
+      <c r="E560" s="4">
         <v>6</v>
       </c>
-      <c r="E560" s="6" t="inlineStr">
+      <c r="F560" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37137,9 +38820,12 @@
         </is>
       </c>
       <c r="D561" s="4">
+        <v>11</v>
+      </c>
+      <c r="E561" s="4">
         <v>7</v>
       </c>
-      <c r="E561" s="6" t="inlineStr">
+      <c r="F561" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37209,9 +38895,12 @@
         </is>
       </c>
       <c r="D562" s="4">
+        <v>11</v>
+      </c>
+      <c r="E562" s="4">
         <v>8</v>
       </c>
-      <c r="E562" s="6" t="inlineStr">
+      <c r="F562" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37281,9 +38970,12 @@
         </is>
       </c>
       <c r="D563" s="4">
+        <v>11</v>
+      </c>
+      <c r="E563" s="4">
         <v>9</v>
       </c>
-      <c r="E563" s="6" t="inlineStr">
+      <c r="F563" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37353,9 +39045,12 @@
         </is>
       </c>
       <c r="D564" s="4">
+        <v>11</v>
+      </c>
+      <c r="E564" s="4">
         <v>10</v>
       </c>
-      <c r="E564" s="6" t="inlineStr">
+      <c r="F564" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37427,7 +39122,10 @@
       <c r="D565" s="4">
         <v>11</v>
       </c>
-      <c r="E565" s="6" t="inlineStr">
+      <c r="E565" s="4">
+        <v>11</v>
+      </c>
+      <c r="F565" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37497,9 +39195,12 @@
         </is>
       </c>
       <c r="D566" s="4">
+        <v>6</v>
+      </c>
+      <c r="E566" s="4">
         <v>1</v>
       </c>
-      <c r="E566" s="6" t="inlineStr">
+      <c r="F566" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37569,9 +39270,12 @@
         </is>
       </c>
       <c r="D567" s="4">
+        <v>6</v>
+      </c>
+      <c r="E567" s="4">
         <v>2</v>
       </c>
-      <c r="E567" s="6" t="inlineStr">
+      <c r="F567" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37641,9 +39345,12 @@
         </is>
       </c>
       <c r="D568" s="4">
+        <v>6</v>
+      </c>
+      <c r="E568" s="4">
         <v>3</v>
       </c>
-      <c r="E568" s="6" t="inlineStr">
+      <c r="F568" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37713,9 +39420,12 @@
         </is>
       </c>
       <c r="D569" s="4">
+        <v>6</v>
+      </c>
+      <c r="E569" s="4">
         <v>4</v>
       </c>
-      <c r="E569" s="6" t="inlineStr">
+      <c r="F569" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37785,9 +39495,12 @@
         </is>
       </c>
       <c r="D570" s="4">
+        <v>6</v>
+      </c>
+      <c r="E570" s="4">
         <v>5</v>
       </c>
-      <c r="E570" s="6" t="inlineStr">
+      <c r="F570" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37859,7 +39572,10 @@
       <c r="D571" s="4">
         <v>6</v>
       </c>
-      <c r="E571" s="6" t="inlineStr">
+      <c r="E571" s="4">
+        <v>6</v>
+      </c>
+      <c r="F571" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37929,9 +39645,12 @@
         </is>
       </c>
       <c r="D572" s="4">
+        <v>5</v>
+      </c>
+      <c r="E572" s="4">
         <v>1</v>
       </c>
-      <c r="E572" s="6" t="inlineStr">
+      <c r="F572" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38001,9 +39720,12 @@
         </is>
       </c>
       <c r="D573" s="4">
+        <v>5</v>
+      </c>
+      <c r="E573" s="4">
         <v>2</v>
       </c>
-      <c r="E573" s="6" t="inlineStr">
+      <c r="F573" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38073,9 +39795,12 @@
         </is>
       </c>
       <c r="D574" s="4">
+        <v>5</v>
+      </c>
+      <c r="E574" s="4">
         <v>3</v>
       </c>
-      <c r="E574" s="6" t="inlineStr">
+      <c r="F574" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38145,9 +39870,12 @@
         </is>
       </c>
       <c r="D575" s="4">
+        <v>5</v>
+      </c>
+      <c r="E575" s="4">
         <v>4</v>
       </c>
-      <c r="E575" s="6" t="inlineStr">
+      <c r="F575" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38219,7 +39947,10 @@
       <c r="D576" s="4">
         <v>5</v>
       </c>
-      <c r="E576" s="6" t="inlineStr">
+      <c r="E576" s="4">
+        <v>5</v>
+      </c>
+      <c r="F576" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38289,9 +40020,12 @@
         </is>
       </c>
       <c r="D577" s="4">
+        <v>109</v>
+      </c>
+      <c r="E577" s="4">
         <v>1</v>
       </c>
-      <c r="E577" s="6" t="inlineStr">
+      <c r="F577" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38361,9 +40095,12 @@
         </is>
       </c>
       <c r="D578" s="4">
+        <v>109</v>
+      </c>
+      <c r="E578" s="4">
         <v>2</v>
       </c>
-      <c r="E578" s="6" t="inlineStr">
+      <c r="F578" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38433,9 +40170,12 @@
         </is>
       </c>
       <c r="D579" s="4">
+        <v>109</v>
+      </c>
+      <c r="E579" s="4">
         <v>3</v>
       </c>
-      <c r="E579" s="6" t="inlineStr">
+      <c r="F579" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38505,9 +40245,12 @@
         </is>
       </c>
       <c r="D580" s="4">
+        <v>109</v>
+      </c>
+      <c r="E580" s="4">
         <v>4</v>
       </c>
-      <c r="E580" s="6" t="inlineStr">
+      <c r="F580" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38577,9 +40320,12 @@
         </is>
       </c>
       <c r="D581" s="4">
+        <v>109</v>
+      </c>
+      <c r="E581" s="4">
         <v>5</v>
       </c>
-      <c r="E581" s="6" t="inlineStr">
+      <c r="F581" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38649,9 +40395,12 @@
         </is>
       </c>
       <c r="D582" s="4">
+        <v>109</v>
+      </c>
+      <c r="E582" s="4">
         <v>6</v>
       </c>
-      <c r="E582" s="6" t="inlineStr">
+      <c r="F582" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38721,9 +40470,12 @@
         </is>
       </c>
       <c r="D583" s="4">
+        <v>109</v>
+      </c>
+      <c r="E583" s="4">
         <v>7</v>
       </c>
-      <c r="E583" s="6" t="inlineStr">
+      <c r="F583" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38793,9 +40545,12 @@
         </is>
       </c>
       <c r="D584" s="4">
+        <v>109</v>
+      </c>
+      <c r="E584" s="4">
         <v>8</v>
       </c>
-      <c r="E584" s="6" t="inlineStr">
+      <c r="F584" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38865,9 +40620,12 @@
         </is>
       </c>
       <c r="D585" s="4">
+        <v>109</v>
+      </c>
+      <c r="E585" s="4">
         <v>9</v>
       </c>
-      <c r="E585" s="6" t="inlineStr">
+      <c r="F585" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38937,9 +40695,12 @@
         </is>
       </c>
       <c r="D586" s="4">
+        <v>109</v>
+      </c>
+      <c r="E586" s="4">
         <v>10</v>
       </c>
-      <c r="E586" s="6" t="inlineStr">
+      <c r="F586" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39009,9 +40770,12 @@
         </is>
       </c>
       <c r="D587" s="4">
+        <v>109</v>
+      </c>
+      <c r="E587" s="4">
         <v>11</v>
       </c>
-      <c r="E587" s="6" t="inlineStr">
+      <c r="F587" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39081,9 +40845,12 @@
         </is>
       </c>
       <c r="D588" s="4">
+        <v>109</v>
+      </c>
+      <c r="E588" s="4">
         <v>12</v>
       </c>
-      <c r="E588" s="6" t="inlineStr">
+      <c r="F588" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39153,9 +40920,12 @@
         </is>
       </c>
       <c r="D589" s="4">
+        <v>109</v>
+      </c>
+      <c r="E589" s="4">
         <v>13</v>
       </c>
-      <c r="E589" s="6" t="inlineStr">
+      <c r="F589" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39225,9 +40995,12 @@
         </is>
       </c>
       <c r="D590" s="4">
+        <v>109</v>
+      </c>
+      <c r="E590" s="4">
         <v>14</v>
       </c>
-      <c r="E590" s="6" t="inlineStr">
+      <c r="F590" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39297,9 +41070,12 @@
         </is>
       </c>
       <c r="D591" s="4">
+        <v>109</v>
+      </c>
+      <c r="E591" s="4">
         <v>15</v>
       </c>
-      <c r="E591" s="6" t="inlineStr">
+      <c r="F591" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39369,9 +41145,12 @@
         </is>
       </c>
       <c r="D592" s="4">
+        <v>109</v>
+      </c>
+      <c r="E592" s="4">
         <v>16</v>
       </c>
-      <c r="E592" s="6" t="inlineStr">
+      <c r="F592" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39441,9 +41220,12 @@
         </is>
       </c>
       <c r="D593" s="4">
+        <v>109</v>
+      </c>
+      <c r="E593" s="4">
         <v>17</v>
       </c>
-      <c r="E593" s="6" t="inlineStr">
+      <c r="F593" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39513,9 +41295,12 @@
         </is>
       </c>
       <c r="D594" s="4">
+        <v>109</v>
+      </c>
+      <c r="E594" s="4">
         <v>18</v>
       </c>
-      <c r="E594" s="6" t="inlineStr">
+      <c r="F594" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39585,9 +41370,12 @@
         </is>
       </c>
       <c r="D595" s="4">
+        <v>109</v>
+      </c>
+      <c r="E595" s="4">
         <v>19</v>
       </c>
-      <c r="E595" s="6" t="inlineStr">
+      <c r="F595" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39657,9 +41445,12 @@
         </is>
       </c>
       <c r="D596" s="4">
+        <v>109</v>
+      </c>
+      <c r="E596" s="4">
         <v>20</v>
       </c>
-      <c r="E596" s="6" t="inlineStr">
+      <c r="F596" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39729,9 +41520,12 @@
         </is>
       </c>
       <c r="D597" s="4">
+        <v>247</v>
+      </c>
+      <c r="E597" s="4">
         <v>1</v>
       </c>
-      <c r="E597" s="6" t="inlineStr">
+      <c r="F597" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39801,9 +41595,12 @@
         </is>
       </c>
       <c r="D598" s="4">
+        <v>247</v>
+      </c>
+      <c r="E598" s="4">
         <v>2</v>
       </c>
-      <c r="E598" s="6" t="inlineStr">
+      <c r="F598" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39873,9 +41670,12 @@
         </is>
       </c>
       <c r="D599" s="4">
+        <v>247</v>
+      </c>
+      <c r="E599" s="4">
         <v>3</v>
       </c>
-      <c r="E599" s="6" t="inlineStr">
+      <c r="F599" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39945,9 +41745,12 @@
         </is>
       </c>
       <c r="D600" s="4">
+        <v>247</v>
+      </c>
+      <c r="E600" s="4">
         <v>4</v>
       </c>
-      <c r="E600" s="6" t="inlineStr">
+      <c r="F600" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40017,9 +41820,12 @@
         </is>
       </c>
       <c r="D601" s="4">
+        <v>247</v>
+      </c>
+      <c r="E601" s="4">
         <v>5</v>
       </c>
-      <c r="E601" s="6" t="inlineStr">
+      <c r="F601" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40089,9 +41895,12 @@
         </is>
       </c>
       <c r="D602" s="4">
+        <v>247</v>
+      </c>
+      <c r="E602" s="4">
         <v>6</v>
       </c>
-      <c r="E602" s="6" t="inlineStr">
+      <c r="F602" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40161,9 +41970,12 @@
         </is>
       </c>
       <c r="D603" s="4">
+        <v>247</v>
+      </c>
+      <c r="E603" s="4">
         <v>7</v>
       </c>
-      <c r="E603" s="6" t="inlineStr">
+      <c r="F603" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40233,9 +42045,12 @@
         </is>
       </c>
       <c r="D604" s="4">
+        <v>247</v>
+      </c>
+      <c r="E604" s="4">
         <v>8</v>
       </c>
-      <c r="E604" s="6" t="inlineStr">
+      <c r="F604" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40305,9 +42120,12 @@
         </is>
       </c>
       <c r="D605" s="4">
+        <v>247</v>
+      </c>
+      <c r="E605" s="4">
         <v>9</v>
       </c>
-      <c r="E605" s="6" t="inlineStr">
+      <c r="F605" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40377,9 +42195,12 @@
         </is>
       </c>
       <c r="D606" s="4">
+        <v>247</v>
+      </c>
+      <c r="E606" s="4">
         <v>10</v>
       </c>
-      <c r="E606" s="6" t="inlineStr">
+      <c r="F606" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40449,9 +42270,12 @@
         </is>
       </c>
       <c r="D607" s="4">
+        <v>247</v>
+      </c>
+      <c r="E607" s="4">
         <v>11</v>
       </c>
-      <c r="E607" s="6" t="inlineStr">
+      <c r="F607" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40521,9 +42345,12 @@
         </is>
       </c>
       <c r="D608" s="4">
+        <v>247</v>
+      </c>
+      <c r="E608" s="4">
         <v>12</v>
       </c>
-      <c r="E608" s="6" t="inlineStr">
+      <c r="F608" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40593,9 +42420,12 @@
         </is>
       </c>
       <c r="D609" s="4">
+        <v>247</v>
+      </c>
+      <c r="E609" s="4">
         <v>13</v>
       </c>
-      <c r="E609" s="6" t="inlineStr">
+      <c r="F609" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40665,9 +42495,12 @@
         </is>
       </c>
       <c r="D610" s="4">
+        <v>247</v>
+      </c>
+      <c r="E610" s="4">
         <v>14</v>
       </c>
-      <c r="E610" s="6" t="inlineStr">
+      <c r="F610" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40737,9 +42570,12 @@
         </is>
       </c>
       <c r="D611" s="4">
+        <v>247</v>
+      </c>
+      <c r="E611" s="4">
         <v>15</v>
       </c>
-      <c r="E611" s="6" t="inlineStr">
+      <c r="F611" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40809,9 +42645,12 @@
         </is>
       </c>
       <c r="D612" s="4">
+        <v>247</v>
+      </c>
+      <c r="E612" s="4">
         <v>16</v>
       </c>
-      <c r="E612" s="6" t="inlineStr">
+      <c r="F612" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40881,9 +42720,12 @@
         </is>
       </c>
       <c r="D613" s="4">
+        <v>247</v>
+      </c>
+      <c r="E613" s="4">
         <v>17</v>
       </c>
-      <c r="E613" s="6" t="inlineStr">
+      <c r="F613" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40953,9 +42795,12 @@
         </is>
       </c>
       <c r="D614" s="4">
+        <v>247</v>
+      </c>
+      <c r="E614" s="4">
         <v>18</v>
       </c>
-      <c r="E614" s="6" t="inlineStr">
+      <c r="F614" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41025,9 +42870,12 @@
         </is>
       </c>
       <c r="D615" s="4">
+        <v>247</v>
+      </c>
+      <c r="E615" s="4">
         <v>19</v>
       </c>
-      <c r="E615" s="6" t="inlineStr">
+      <c r="F615" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41097,9 +42945,12 @@
         </is>
       </c>
       <c r="D616" s="4">
+        <v>247</v>
+      </c>
+      <c r="E616" s="4">
         <v>20</v>
       </c>
-      <c r="E616" s="6" t="inlineStr">
+      <c r="F616" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41169,9 +43020,12 @@
         </is>
       </c>
       <c r="D617" s="4">
+        <v>178</v>
+      </c>
+      <c r="E617" s="4">
         <v>1</v>
       </c>
-      <c r="E617" s="6" t="inlineStr">
+      <c r="F617" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41241,9 +43095,12 @@
         </is>
       </c>
       <c r="D618" s="4">
+        <v>178</v>
+      </c>
+      <c r="E618" s="4">
         <v>2</v>
       </c>
-      <c r="E618" s="6" t="inlineStr">
+      <c r="F618" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41313,9 +43170,12 @@
         </is>
       </c>
       <c r="D619" s="4">
+        <v>178</v>
+      </c>
+      <c r="E619" s="4">
         <v>3</v>
       </c>
-      <c r="E619" s="6" t="inlineStr">
+      <c r="F619" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41385,9 +43245,12 @@
         </is>
       </c>
       <c r="D620" s="4">
+        <v>178</v>
+      </c>
+      <c r="E620" s="4">
         <v>4</v>
       </c>
-      <c r="E620" s="6" t="inlineStr">
+      <c r="F620" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41457,9 +43320,12 @@
         </is>
       </c>
       <c r="D621" s="4">
+        <v>178</v>
+      </c>
+      <c r="E621" s="4">
         <v>5</v>
       </c>
-      <c r="E621" s="6" t="inlineStr">
+      <c r="F621" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41529,9 +43395,12 @@
         </is>
       </c>
       <c r="D622" s="4">
+        <v>178</v>
+      </c>
+      <c r="E622" s="4">
         <v>6</v>
       </c>
-      <c r="E622" s="6" t="inlineStr">
+      <c r="F622" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41601,9 +43470,12 @@
         </is>
       </c>
       <c r="D623" s="4">
+        <v>178</v>
+      </c>
+      <c r="E623" s="4">
         <v>7</v>
       </c>
-      <c r="E623" s="6" t="inlineStr">
+      <c r="F623" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41673,9 +43545,12 @@
         </is>
       </c>
       <c r="D624" s="4">
+        <v>178</v>
+      </c>
+      <c r="E624" s="4">
         <v>8</v>
       </c>
-      <c r="E624" s="6" t="inlineStr">
+      <c r="F624" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41745,9 +43620,12 @@
         </is>
       </c>
       <c r="D625" s="4">
+        <v>178</v>
+      </c>
+      <c r="E625" s="4">
         <v>9</v>
       </c>
-      <c r="E625" s="6" t="inlineStr">
+      <c r="F625" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41817,9 +43695,12 @@
         </is>
       </c>
       <c r="D626" s="4">
+        <v>178</v>
+      </c>
+      <c r="E626" s="4">
         <v>10</v>
       </c>
-      <c r="E626" s="6" t="inlineStr">
+      <c r="F626" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41889,9 +43770,12 @@
         </is>
       </c>
       <c r="D627" s="4">
+        <v>178</v>
+      </c>
+      <c r="E627" s="4">
         <v>11</v>
       </c>
-      <c r="E627" s="6" t="inlineStr">
+      <c r="F627" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41961,9 +43845,12 @@
         </is>
       </c>
       <c r="D628" s="4">
+        <v>178</v>
+      </c>
+      <c r="E628" s="4">
         <v>12</v>
       </c>
-      <c r="E628" s="6" t="inlineStr">
+      <c r="F628" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -42033,9 +43920,12 @@
         </is>
       </c>
       <c r="D629" s="4">
+        <v>178</v>
+      </c>
+      <c r="E629" s="4">
         <v>13</v>
       </c>
-      <c r="E629" s="6" t="inlineStr">
+      <c r="F629" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -42105,9 +43995,12 @@
         </is>
       </c>
       <c r="D630" s="4">
+        <v>178</v>
+      </c>
+      <c r="E630" s="4">
         <v>14</v>
       </c>
-      <c r="E630" s="6" t="inlineStr">
+      <c r="F630" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -42177,9 +44070,12 @@
         </is>
       </c>
       <c r="D631" s="4">
+        <v>178</v>
+      </c>
+      <c r="E631" s="4">
         <v>15</v>
       </c>
-      <c r="E631" s="6" t="inlineStr">
+      <c r="F631" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -42249,9 +44145,12 @@
         </is>
       </c>
       <c r="D632" s="4">
+        <v>178</v>
+      </c>
+      <c r="E632" s="4">
         <v>16</v>
       </c>
-      <c r="E632" s="6" t="inlineStr">
+      <c r="F632" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -42321,9 +44220,12 @@
         </is>
       </c>
       <c r="D633" s="4">
+        <v>178</v>
+      </c>
+      <c r="E633" s="4">
         <v>17</v>
       </c>
-      <c r="E633" s="6" t="inlineStr">
+      <c r="F633" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -42393,9 +44295,12 @@
         </is>
       </c>
       <c r="D634" s="4">
+        <v>178</v>
+      </c>
+      <c r="E634" s="4">
         <v>18</v>
       </c>
-      <c r="E634" s="6" t="inlineStr">
+      <c r="F634" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -42465,9 +44370,12 @@
         </is>
       </c>
       <c r="D635" s="4">
+        <v>178</v>
+      </c>
+      <c r="E635" s="4">
         <v>19</v>
       </c>
-      <c r="E635" s="6" t="inlineStr">
+      <c r="F635" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -42537,9 +44445,12 @@
         </is>
       </c>
       <c r="D636" s="4">
+        <v>178</v>
+      </c>
+      <c r="E636" s="4">
         <v>20</v>
       </c>
-      <c r="E636" s="6" t="inlineStr">
+      <c r="F636" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -42609,9 +44520,12 @@
         </is>
       </c>
       <c r="D637" s="4">
+        <v>98</v>
+      </c>
+      <c r="E637" s="4">
         <v>1</v>
       </c>
-      <c r="E637" s="6" t="inlineStr">
+      <c r="F637" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -42681,9 +44595,12 @@
         </is>
       </c>
       <c r="D638" s="4">
+        <v>98</v>
+      </c>
+      <c r="E638" s="4">
         <v>2</v>
       </c>
-      <c r="E638" s="6" t="inlineStr">
+      <c r="F638" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -42753,9 +44670,12 @@
         </is>
       </c>
       <c r="D639" s="4">
+        <v>98</v>
+      </c>
+      <c r="E639" s="4">
         <v>3</v>
       </c>
-      <c r="E639" s="6" t="inlineStr">
+      <c r="F639" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -42825,9 +44745,12 @@
         </is>
       </c>
       <c r="D640" s="4">
+        <v>98</v>
+      </c>
+      <c r="E640" s="4">
         <v>4</v>
       </c>
-      <c r="E640" s="6" t="inlineStr">
+      <c r="F640" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -42897,9 +44820,12 @@
         </is>
       </c>
       <c r="D641" s="4">
+        <v>98</v>
+      </c>
+      <c r="E641" s="4">
         <v>5</v>
       </c>
-      <c r="E641" s="6" t="inlineStr">
+      <c r="F641" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -42969,9 +44895,12 @@
         </is>
       </c>
       <c r="D642" s="4">
+        <v>98</v>
+      </c>
+      <c r="E642" s="4">
         <v>6</v>
       </c>
-      <c r="E642" s="6" t="inlineStr">
+      <c r="F642" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -43041,9 +44970,12 @@
         </is>
       </c>
       <c r="D643" s="4">
+        <v>98</v>
+      </c>
+      <c r="E643" s="4">
         <v>7</v>
       </c>
-      <c r="E643" s="6" t="inlineStr">
+      <c r="F643" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -43113,9 +45045,12 @@
         </is>
       </c>
       <c r="D644" s="4">
+        <v>98</v>
+      </c>
+      <c r="E644" s="4">
         <v>8</v>
       </c>
-      <c r="E644" s="6" t="inlineStr">
+      <c r="F644" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -43185,9 +45120,12 @@
         </is>
       </c>
       <c r="D645" s="4">
+        <v>98</v>
+      </c>
+      <c r="E645" s="4">
         <v>9</v>
       </c>
-      <c r="E645" s="6" t="inlineStr">
+      <c r="F645" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -43257,9 +45195,12 @@
         </is>
       </c>
       <c r="D646" s="4">
+        <v>98</v>
+      </c>
+      <c r="E646" s="4">
         <v>10</v>
       </c>
-      <c r="E646" s="6" t="inlineStr">
+      <c r="F646" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -43329,9 +45270,12 @@
         </is>
       </c>
       <c r="D647" s="4">
+        <v>98</v>
+      </c>
+      <c r="E647" s="4">
         <v>11</v>
       </c>
-      <c r="E647" s="6" t="inlineStr">
+      <c r="F647" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -43401,9 +45345,12 @@
         </is>
       </c>
       <c r="D648" s="4">
+        <v>98</v>
+      </c>
+      <c r="E648" s="4">
         <v>12</v>
       </c>
-      <c r="E648" s="6" t="inlineStr">
+      <c r="F648" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -43473,9 +45420,12 @@
         </is>
       </c>
       <c r="D649" s="4">
+        <v>98</v>
+      </c>
+      <c r="E649" s="4">
         <v>13</v>
       </c>
-      <c r="E649" s="6" t="inlineStr">
+      <c r="F649" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -43545,9 +45495,12 @@
         </is>
       </c>
       <c r="D650" s="4">
+        <v>98</v>
+      </c>
+      <c r="E650" s="4">
         <v>14</v>
       </c>
-      <c r="E650" s="6" t="inlineStr">
+      <c r="F650" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -43617,9 +45570,12 @@
         </is>
       </c>
       <c r="D651" s="4">
+        <v>98</v>
+      </c>
+      <c r="E651" s="4">
         <v>15</v>
       </c>
-      <c r="E651" s="6" t="inlineStr">
+      <c r="F651" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -43689,9 +45645,12 @@
         </is>
       </c>
       <c r="D652" s="4">
+        <v>98</v>
+      </c>
+      <c r="E652" s="4">
         <v>16</v>
       </c>
-      <c r="E652" s="6" t="inlineStr">
+      <c r="F652" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -43761,9 +45720,12 @@
         </is>
       </c>
       <c r="D653" s="4">
+        <v>98</v>
+      </c>
+      <c r="E653" s="4">
         <v>17</v>
       </c>
-      <c r="E653" s="6" t="inlineStr">
+      <c r="F653" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -43833,9 +45795,12 @@
         </is>
       </c>
       <c r="D654" s="4">
+        <v>98</v>
+      </c>
+      <c r="E654" s="4">
         <v>18</v>
       </c>
-      <c r="E654" s="6" t="inlineStr">
+      <c r="F654" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -43905,9 +45870,12 @@
         </is>
       </c>
       <c r="D655" s="4">
+        <v>98</v>
+      </c>
+      <c r="E655" s="4">
         <v>19</v>
       </c>
-      <c r="E655" s="6" t="inlineStr">
+      <c r="F655" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -43977,9 +45945,12 @@
         </is>
       </c>
       <c r="D656" s="4">
+        <v>98</v>
+      </c>
+      <c r="E656" s="4">
         <v>20</v>
       </c>
-      <c r="E656" s="6" t="inlineStr">
+      <c r="F656" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -44049,9 +46020,12 @@
         </is>
       </c>
       <c r="D657" s="4">
+        <v>52</v>
+      </c>
+      <c r="E657" s="4">
         <v>1</v>
       </c>
-      <c r="E657" s="6" t="inlineStr">
+      <c r="F657" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -44121,9 +46095,12 @@
         </is>
       </c>
       <c r="D658" s="4">
+        <v>52</v>
+      </c>
+      <c r="E658" s="4">
         <v>2</v>
       </c>
-      <c r="E658" s="6" t="inlineStr">
+      <c r="F658" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -44193,9 +46170,12 @@
         </is>
       </c>
       <c r="D659" s="4">
+        <v>52</v>
+      </c>
+      <c r="E659" s="4">
         <v>3</v>
       </c>
-      <c r="E659" s="6" t="inlineStr">
+      <c r="F659" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -44265,9 +46245,12 @@
         </is>
       </c>
       <c r="D660" s="4">
+        <v>52</v>
+      </c>
+      <c r="E660" s="4">
         <v>4</v>
       </c>
-      <c r="E660" s="6" t="inlineStr">
+      <c r="F660" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -44337,9 +46320,12 @@
         </is>
       </c>
       <c r="D661" s="4">
+        <v>52</v>
+      </c>
+      <c r="E661" s="4">
         <v>5</v>
       </c>
-      <c r="E661" s="6" t="inlineStr">
+      <c r="F661" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -44409,9 +46395,12 @@
         </is>
       </c>
       <c r="D662" s="4">
+        <v>52</v>
+      </c>
+      <c r="E662" s="4">
         <v>6</v>
       </c>
-      <c r="E662" s="6" t="inlineStr">
+      <c r="F662" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -44481,9 +46470,12 @@
         </is>
       </c>
       <c r="D663" s="4">
+        <v>52</v>
+      </c>
+      <c r="E663" s="4">
         <v>7</v>
       </c>
-      <c r="E663" s="6" t="inlineStr">
+      <c r="F663" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -44553,9 +46545,12 @@
         </is>
       </c>
       <c r="D664" s="4">
+        <v>52</v>
+      </c>
+      <c r="E664" s="4">
         <v>8</v>
       </c>
-      <c r="E664" s="6" t="inlineStr">
+      <c r="F664" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -44625,9 +46620,12 @@
         </is>
       </c>
       <c r="D665" s="4">
+        <v>52</v>
+      </c>
+      <c r="E665" s="4">
         <v>9</v>
       </c>
-      <c r="E665" s="6" t="inlineStr">
+      <c r="F665" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -44697,9 +46695,12 @@
         </is>
       </c>
       <c r="D666" s="4">
+        <v>52</v>
+      </c>
+      <c r="E666" s="4">
         <v>10</v>
       </c>
-      <c r="E666" s="6" t="inlineStr">
+      <c r="F666" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -44769,9 +46770,12 @@
         </is>
       </c>
       <c r="D667" s="4">
+        <v>52</v>
+      </c>
+      <c r="E667" s="4">
         <v>11</v>
       </c>
-      <c r="E667" s="6" t="inlineStr">
+      <c r="F667" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -44841,9 +46845,12 @@
         </is>
       </c>
       <c r="D668" s="4">
+        <v>52</v>
+      </c>
+      <c r="E668" s="4">
         <v>12</v>
       </c>
-      <c r="E668" s="6" t="inlineStr">
+      <c r="F668" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -44913,9 +46920,12 @@
         </is>
       </c>
       <c r="D669" s="4">
+        <v>52</v>
+      </c>
+      <c r="E669" s="4">
         <v>13</v>
       </c>
-      <c r="E669" s="6" t="inlineStr">
+      <c r="F669" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -44985,9 +46995,12 @@
         </is>
       </c>
       <c r="D670" s="4">
+        <v>52</v>
+      </c>
+      <c r="E670" s="4">
         <v>14</v>
       </c>
-      <c r="E670" s="6" t="inlineStr">
+      <c r="F670" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -45057,9 +47070,12 @@
         </is>
       </c>
       <c r="D671" s="4">
+        <v>52</v>
+      </c>
+      <c r="E671" s="4">
         <v>15</v>
       </c>
-      <c r="E671" s="6" t="inlineStr">
+      <c r="F671" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -45129,9 +47145,12 @@
         </is>
       </c>
       <c r="D672" s="4">
+        <v>52</v>
+      </c>
+      <c r="E672" s="4">
         <v>16</v>
       </c>
-      <c r="E672" s="6" t="inlineStr">
+      <c r="F672" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -45201,9 +47220,12 @@
         </is>
       </c>
       <c r="D673" s="4">
+        <v>52</v>
+      </c>
+      <c r="E673" s="4">
         <v>17</v>
       </c>
-      <c r="E673" s="6" t="inlineStr">
+      <c r="F673" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -45273,9 +47295,12 @@
         </is>
       </c>
       <c r="D674" s="4">
+        <v>52</v>
+      </c>
+      <c r="E674" s="4">
         <v>18</v>
       </c>
-      <c r="E674" s="6" t="inlineStr">
+      <c r="F674" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -45345,9 +47370,12 @@
         </is>
       </c>
       <c r="D675" s="4">
+        <v>52</v>
+      </c>
+      <c r="E675" s="4">
         <v>19</v>
       </c>
-      <c r="E675" s="6" t="inlineStr">
+      <c r="F675" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -45417,9 +47445,12 @@
         </is>
       </c>
       <c r="D676" s="4">
+        <v>52</v>
+      </c>
+      <c r="E676" s="4">
         <v>20</v>
       </c>
-      <c r="E676" s="6" t="inlineStr">
+      <c r="F676" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -45489,9 +47520,12 @@
         </is>
       </c>
       <c r="D677" s="4">
+        <v>48</v>
+      </c>
+      <c r="E677" s="4">
         <v>1</v>
       </c>
-      <c r="E677" s="6" t="inlineStr">
+      <c r="F677" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -45561,9 +47595,12 @@
         </is>
       </c>
       <c r="D678" s="4">
+        <v>48</v>
+      </c>
+      <c r="E678" s="4">
         <v>2</v>
       </c>
-      <c r="E678" s="6" t="inlineStr">
+      <c r="F678" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -45633,9 +47670,12 @@
         </is>
       </c>
       <c r="D679" s="4">
+        <v>48</v>
+      </c>
+      <c r="E679" s="4">
         <v>3</v>
       </c>
-      <c r="E679" s="6" t="inlineStr">
+      <c r="F679" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -45705,9 +47745,12 @@
         </is>
       </c>
       <c r="D680" s="4">
+        <v>48</v>
+      </c>
+      <c r="E680" s="4">
         <v>4</v>
       </c>
-      <c r="E680" s="6" t="inlineStr">
+      <c r="F680" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -45777,9 +47820,12 @@
         </is>
       </c>
       <c r="D681" s="4">
+        <v>48</v>
+      </c>
+      <c r="E681" s="4">
         <v>5</v>
       </c>
-      <c r="E681" s="6" t="inlineStr">
+      <c r="F681" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -45849,9 +47895,12 @@
         </is>
       </c>
       <c r="D682" s="4">
+        <v>48</v>
+      </c>
+      <c r="E682" s="4">
         <v>6</v>
       </c>
-      <c r="E682" s="6" t="inlineStr">
+      <c r="F682" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -45921,9 +47970,12 @@
         </is>
       </c>
       <c r="D683" s="4">
+        <v>48</v>
+      </c>
+      <c r="E683" s="4">
         <v>7</v>
       </c>
-      <c r="E683" s="6" t="inlineStr">
+      <c r="F683" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -45993,9 +48045,12 @@
         </is>
       </c>
       <c r="D684" s="4">
+        <v>48</v>
+      </c>
+      <c r="E684" s="4">
         <v>8</v>
       </c>
-      <c r="E684" s="6" t="inlineStr">
+      <c r="F684" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -46065,9 +48120,12 @@
         </is>
       </c>
       <c r="D685" s="4">
+        <v>48</v>
+      </c>
+      <c r="E685" s="4">
         <v>9</v>
       </c>
-      <c r="E685" s="6" t="inlineStr">
+      <c r="F685" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -46137,9 +48195,12 @@
         </is>
       </c>
       <c r="D686" s="4">
+        <v>48</v>
+      </c>
+      <c r="E686" s="4">
         <v>10</v>
       </c>
-      <c r="E686" s="6" t="inlineStr">
+      <c r="F686" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -46209,9 +48270,12 @@
         </is>
       </c>
       <c r="D687" s="4">
+        <v>48</v>
+      </c>
+      <c r="E687" s="4">
         <v>11</v>
       </c>
-      <c r="E687" s="6" t="inlineStr">
+      <c r="F687" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -46281,9 +48345,12 @@
         </is>
       </c>
       <c r="D688" s="4">
+        <v>48</v>
+      </c>
+      <c r="E688" s="4">
         <v>12</v>
       </c>
-      <c r="E688" s="6" t="inlineStr">
+      <c r="F688" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -46353,9 +48420,12 @@
         </is>
       </c>
       <c r="D689" s="4">
+        <v>48</v>
+      </c>
+      <c r="E689" s="4">
         <v>13</v>
       </c>
-      <c r="E689" s="6" t="inlineStr">
+      <c r="F689" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -46425,9 +48495,12 @@
         </is>
       </c>
       <c r="D690" s="4">
+        <v>48</v>
+      </c>
+      <c r="E690" s="4">
         <v>14</v>
       </c>
-      <c r="E690" s="6" t="inlineStr">
+      <c r="F690" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -46497,9 +48570,12 @@
         </is>
       </c>
       <c r="D691" s="4">
+        <v>48</v>
+      </c>
+      <c r="E691" s="4">
         <v>15</v>
       </c>
-      <c r="E691" s="6" t="inlineStr">
+      <c r="F691" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -46569,9 +48645,12 @@
         </is>
       </c>
       <c r="D692" s="4">
+        <v>48</v>
+      </c>
+      <c r="E692" s="4">
         <v>16</v>
       </c>
-      <c r="E692" s="6" t="inlineStr">
+      <c r="F692" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -46641,9 +48720,12 @@
         </is>
       </c>
       <c r="D693" s="4">
+        <v>48</v>
+      </c>
+      <c r="E693" s="4">
         <v>17</v>
       </c>
-      <c r="E693" s="6" t="inlineStr">
+      <c r="F693" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -46713,9 +48795,12 @@
         </is>
       </c>
       <c r="D694" s="4">
+        <v>48</v>
+      </c>
+      <c r="E694" s="4">
         <v>18</v>
       </c>
-      <c r="E694" s="6" t="inlineStr">
+      <c r="F694" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -46785,9 +48870,12 @@
         </is>
       </c>
       <c r="D695" s="4">
+        <v>48</v>
+      </c>
+      <c r="E695" s="4">
         <v>19</v>
       </c>
-      <c r="E695" s="6" t="inlineStr">
+      <c r="F695" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -46857,9 +48945,12 @@
         </is>
       </c>
       <c r="D696" s="4">
+        <v>48</v>
+      </c>
+      <c r="E696" s="4">
         <v>20</v>
       </c>
-      <c r="E696" s="6" t="inlineStr">
+      <c r="F696" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -46913,304 +49004,403 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="297">
+  <mergeCells count="396">
     <mergeCell ref="A2:A6"/>
     <mergeCell ref="B2:B6"/>
     <mergeCell ref="C2:C6"/>
+    <mergeCell ref="D2:D6"/>
     <mergeCell ref="A8:A12"/>
     <mergeCell ref="B8:B12"/>
     <mergeCell ref="C8:C12"/>
+    <mergeCell ref="D8:D12"/>
     <mergeCell ref="A14:A15"/>
     <mergeCell ref="B14:B15"/>
     <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
     <mergeCell ref="A17:A18"/>
     <mergeCell ref="B17:B18"/>
     <mergeCell ref="C17:C18"/>
+    <mergeCell ref="D17:D18"/>
     <mergeCell ref="A25:A29"/>
     <mergeCell ref="B25:B29"/>
     <mergeCell ref="C25:C29"/>
+    <mergeCell ref="D25:D29"/>
     <mergeCell ref="A31:A32"/>
     <mergeCell ref="B31:B32"/>
     <mergeCell ref="C31:C32"/>
+    <mergeCell ref="D31:D32"/>
     <mergeCell ref="A34:A35"/>
     <mergeCell ref="B34:B35"/>
     <mergeCell ref="C34:C35"/>
+    <mergeCell ref="D34:D35"/>
     <mergeCell ref="A40:A42"/>
     <mergeCell ref="B40:B42"/>
     <mergeCell ref="C40:C42"/>
+    <mergeCell ref="D40:D42"/>
     <mergeCell ref="A44:A48"/>
     <mergeCell ref="B44:B48"/>
     <mergeCell ref="C44:C48"/>
+    <mergeCell ref="D44:D48"/>
     <mergeCell ref="A49:A51"/>
     <mergeCell ref="B49:B51"/>
     <mergeCell ref="C49:C51"/>
+    <mergeCell ref="D49:D51"/>
     <mergeCell ref="A52:A55"/>
     <mergeCell ref="B52:B55"/>
     <mergeCell ref="C52:C55"/>
+    <mergeCell ref="D52:D55"/>
     <mergeCell ref="A56:A58"/>
     <mergeCell ref="B56:B58"/>
     <mergeCell ref="C56:C58"/>
+    <mergeCell ref="D56:D58"/>
     <mergeCell ref="A60:A61"/>
     <mergeCell ref="B60:B61"/>
     <mergeCell ref="C60:C61"/>
+    <mergeCell ref="D60:D61"/>
     <mergeCell ref="A67:A70"/>
     <mergeCell ref="B67:B70"/>
     <mergeCell ref="C67:C70"/>
+    <mergeCell ref="D67:D70"/>
     <mergeCell ref="A71:A75"/>
     <mergeCell ref="B71:B75"/>
     <mergeCell ref="C71:C75"/>
+    <mergeCell ref="D71:D75"/>
     <mergeCell ref="A80:A81"/>
     <mergeCell ref="B80:B81"/>
     <mergeCell ref="C80:C81"/>
+    <mergeCell ref="D80:D81"/>
     <mergeCell ref="A84:A86"/>
     <mergeCell ref="B84:B86"/>
     <mergeCell ref="C84:C86"/>
+    <mergeCell ref="D84:D86"/>
     <mergeCell ref="A87:A88"/>
     <mergeCell ref="B87:B88"/>
     <mergeCell ref="C87:C88"/>
+    <mergeCell ref="D87:D88"/>
     <mergeCell ref="A89:A90"/>
     <mergeCell ref="B89:B90"/>
     <mergeCell ref="C89:C90"/>
+    <mergeCell ref="D89:D90"/>
     <mergeCell ref="A91:A93"/>
     <mergeCell ref="B91:B93"/>
     <mergeCell ref="C91:C93"/>
+    <mergeCell ref="D91:D93"/>
     <mergeCell ref="A95:A96"/>
     <mergeCell ref="B95:B96"/>
     <mergeCell ref="C95:C96"/>
+    <mergeCell ref="D95:D96"/>
     <mergeCell ref="A97:A98"/>
     <mergeCell ref="B97:B98"/>
     <mergeCell ref="C97:C98"/>
+    <mergeCell ref="D97:D98"/>
     <mergeCell ref="A102:A104"/>
     <mergeCell ref="B102:B104"/>
     <mergeCell ref="C102:C104"/>
+    <mergeCell ref="D102:D104"/>
     <mergeCell ref="A106:A107"/>
     <mergeCell ref="B106:B107"/>
     <mergeCell ref="C106:C107"/>
+    <mergeCell ref="D106:D107"/>
     <mergeCell ref="A110:A112"/>
     <mergeCell ref="B110:B112"/>
     <mergeCell ref="C110:C112"/>
+    <mergeCell ref="D110:D112"/>
     <mergeCell ref="A113:A114"/>
     <mergeCell ref="B113:B114"/>
     <mergeCell ref="C113:C114"/>
+    <mergeCell ref="D113:D114"/>
     <mergeCell ref="A115:A119"/>
     <mergeCell ref="B115:B119"/>
     <mergeCell ref="C115:C119"/>
+    <mergeCell ref="D115:D119"/>
     <mergeCell ref="A120:A122"/>
     <mergeCell ref="B120:B122"/>
     <mergeCell ref="C120:C122"/>
+    <mergeCell ref="D120:D122"/>
     <mergeCell ref="A126:A129"/>
     <mergeCell ref="B126:B129"/>
     <mergeCell ref="C126:C129"/>
+    <mergeCell ref="D126:D129"/>
     <mergeCell ref="A130:A131"/>
     <mergeCell ref="B130:B131"/>
     <mergeCell ref="C130:C131"/>
+    <mergeCell ref="D130:D131"/>
     <mergeCell ref="A132:A133"/>
     <mergeCell ref="B132:B133"/>
     <mergeCell ref="C132:C133"/>
+    <mergeCell ref="D132:D133"/>
     <mergeCell ref="A134:A135"/>
     <mergeCell ref="B134:B135"/>
     <mergeCell ref="C134:C135"/>
+    <mergeCell ref="D134:D135"/>
     <mergeCell ref="A136:A137"/>
     <mergeCell ref="B136:B137"/>
     <mergeCell ref="C136:C137"/>
+    <mergeCell ref="D136:D137"/>
     <mergeCell ref="A148:A150"/>
     <mergeCell ref="B148:B150"/>
     <mergeCell ref="C148:C150"/>
+    <mergeCell ref="D148:D150"/>
     <mergeCell ref="A156:A157"/>
     <mergeCell ref="B156:B157"/>
     <mergeCell ref="C156:C157"/>
+    <mergeCell ref="D156:D157"/>
     <mergeCell ref="A161:A162"/>
     <mergeCell ref="B161:B162"/>
     <mergeCell ref="C161:C162"/>
+    <mergeCell ref="D161:D162"/>
     <mergeCell ref="A167:A168"/>
     <mergeCell ref="B167:B168"/>
     <mergeCell ref="C167:C168"/>
+    <mergeCell ref="D167:D168"/>
     <mergeCell ref="A173:A175"/>
     <mergeCell ref="B173:B175"/>
     <mergeCell ref="C173:C175"/>
+    <mergeCell ref="D173:D175"/>
     <mergeCell ref="A179:A180"/>
     <mergeCell ref="B179:B180"/>
     <mergeCell ref="C179:C180"/>
+    <mergeCell ref="D179:D180"/>
     <mergeCell ref="A187:A189"/>
     <mergeCell ref="B187:B189"/>
     <mergeCell ref="C187:C189"/>
+    <mergeCell ref="D187:D189"/>
     <mergeCell ref="A191:A192"/>
     <mergeCell ref="B191:B192"/>
     <mergeCell ref="C191:C192"/>
+    <mergeCell ref="D191:D192"/>
     <mergeCell ref="A195:A196"/>
     <mergeCell ref="B195:B196"/>
     <mergeCell ref="C195:C196"/>
+    <mergeCell ref="D195:D196"/>
     <mergeCell ref="A205:A207"/>
     <mergeCell ref="B205:B207"/>
     <mergeCell ref="C205:C207"/>
+    <mergeCell ref="D205:D207"/>
     <mergeCell ref="A223:A224"/>
     <mergeCell ref="B223:B224"/>
     <mergeCell ref="C223:C224"/>
+    <mergeCell ref="D223:D224"/>
     <mergeCell ref="A233:A234"/>
     <mergeCell ref="B233:B234"/>
     <mergeCell ref="C233:C234"/>
+    <mergeCell ref="D233:D234"/>
     <mergeCell ref="A237:A243"/>
     <mergeCell ref="B237:B243"/>
     <mergeCell ref="C237:C243"/>
+    <mergeCell ref="D237:D243"/>
     <mergeCell ref="A244:A247"/>
     <mergeCell ref="B244:B247"/>
     <mergeCell ref="C244:C247"/>
+    <mergeCell ref="D244:D247"/>
     <mergeCell ref="A249:A253"/>
     <mergeCell ref="B249:B253"/>
     <mergeCell ref="C249:C253"/>
+    <mergeCell ref="D249:D253"/>
     <mergeCell ref="A257:A259"/>
     <mergeCell ref="B257:B259"/>
     <mergeCell ref="C257:C259"/>
+    <mergeCell ref="D257:D259"/>
     <mergeCell ref="A260:A276"/>
     <mergeCell ref="B260:B276"/>
     <mergeCell ref="C260:C276"/>
+    <mergeCell ref="D260:D276"/>
     <mergeCell ref="A277:A283"/>
     <mergeCell ref="B277:B283"/>
     <mergeCell ref="C277:C283"/>
+    <mergeCell ref="D277:D283"/>
     <mergeCell ref="A284:A287"/>
     <mergeCell ref="B284:B287"/>
     <mergeCell ref="C284:C287"/>
+    <mergeCell ref="D284:D287"/>
     <mergeCell ref="A288:A295"/>
     <mergeCell ref="B288:B295"/>
     <mergeCell ref="C288:C295"/>
+    <mergeCell ref="D288:D295"/>
     <mergeCell ref="A296:A300"/>
     <mergeCell ref="B296:B300"/>
     <mergeCell ref="C296:C300"/>
+    <mergeCell ref="D296:D300"/>
     <mergeCell ref="A301:A305"/>
     <mergeCell ref="B301:B305"/>
     <mergeCell ref="C301:C305"/>
+    <mergeCell ref="D301:D305"/>
     <mergeCell ref="A306:A309"/>
     <mergeCell ref="B306:B309"/>
     <mergeCell ref="C306:C309"/>
+    <mergeCell ref="D306:D309"/>
     <mergeCell ref="A310:A312"/>
     <mergeCell ref="B310:B312"/>
     <mergeCell ref="C310:C312"/>
+    <mergeCell ref="D310:D312"/>
     <mergeCell ref="A313:A317"/>
     <mergeCell ref="B313:B317"/>
     <mergeCell ref="C313:C317"/>
+    <mergeCell ref="D313:D317"/>
     <mergeCell ref="A318:A337"/>
     <mergeCell ref="B318:B337"/>
     <mergeCell ref="C318:C337"/>
+    <mergeCell ref="D318:D337"/>
     <mergeCell ref="A338:A343"/>
     <mergeCell ref="B338:B343"/>
     <mergeCell ref="C338:C343"/>
+    <mergeCell ref="D338:D343"/>
     <mergeCell ref="A344:A347"/>
     <mergeCell ref="B344:B347"/>
     <mergeCell ref="C344:C347"/>
+    <mergeCell ref="D344:D347"/>
     <mergeCell ref="A349:A358"/>
     <mergeCell ref="B349:B358"/>
     <mergeCell ref="C349:C358"/>
+    <mergeCell ref="D349:D358"/>
     <mergeCell ref="A359:A362"/>
     <mergeCell ref="B359:B362"/>
     <mergeCell ref="C359:C362"/>
+    <mergeCell ref="D359:D362"/>
     <mergeCell ref="A363:A366"/>
     <mergeCell ref="B363:B366"/>
     <mergeCell ref="C363:C366"/>
+    <mergeCell ref="D363:D366"/>
     <mergeCell ref="A367:A370"/>
     <mergeCell ref="B367:B370"/>
     <mergeCell ref="C367:C370"/>
+    <mergeCell ref="D367:D370"/>
     <mergeCell ref="A372:A380"/>
     <mergeCell ref="B372:B380"/>
     <mergeCell ref="C372:C380"/>
+    <mergeCell ref="D372:D380"/>
     <mergeCell ref="A381:A382"/>
     <mergeCell ref="B381:B382"/>
     <mergeCell ref="C381:C382"/>
+    <mergeCell ref="D381:D382"/>
     <mergeCell ref="A383:A385"/>
     <mergeCell ref="B383:B385"/>
     <mergeCell ref="C383:C385"/>
+    <mergeCell ref="D383:D385"/>
     <mergeCell ref="A386:A387"/>
     <mergeCell ref="B386:B387"/>
     <mergeCell ref="C386:C387"/>
+    <mergeCell ref="D386:D387"/>
     <mergeCell ref="A388:A389"/>
     <mergeCell ref="B388:B389"/>
     <mergeCell ref="C388:C389"/>
+    <mergeCell ref="D388:D389"/>
     <mergeCell ref="A391:A397"/>
     <mergeCell ref="B391:B397"/>
     <mergeCell ref="C391:C397"/>
+    <mergeCell ref="D391:D397"/>
     <mergeCell ref="A398:A400"/>
     <mergeCell ref="B398:B400"/>
     <mergeCell ref="C398:C400"/>
+    <mergeCell ref="D398:D400"/>
     <mergeCell ref="A401:A402"/>
     <mergeCell ref="B401:B402"/>
     <mergeCell ref="C401:C402"/>
+    <mergeCell ref="D401:D402"/>
     <mergeCell ref="A405:A406"/>
     <mergeCell ref="B405:B406"/>
     <mergeCell ref="C405:C406"/>
+    <mergeCell ref="D405:D406"/>
     <mergeCell ref="A407:A412"/>
     <mergeCell ref="B407:B412"/>
     <mergeCell ref="C407:C412"/>
+    <mergeCell ref="D407:D412"/>
     <mergeCell ref="A413:A422"/>
     <mergeCell ref="B413:B422"/>
     <mergeCell ref="C413:C422"/>
+    <mergeCell ref="D413:D422"/>
     <mergeCell ref="A425:A428"/>
     <mergeCell ref="B425:B428"/>
     <mergeCell ref="C425:C428"/>
+    <mergeCell ref="D425:D428"/>
     <mergeCell ref="A438:A448"/>
     <mergeCell ref="B438:B448"/>
     <mergeCell ref="C438:C448"/>
+    <mergeCell ref="D438:D448"/>
     <mergeCell ref="A450:A458"/>
     <mergeCell ref="B450:B458"/>
     <mergeCell ref="C450:C458"/>
+    <mergeCell ref="D450:D458"/>
     <mergeCell ref="A459:A462"/>
     <mergeCell ref="B459:B462"/>
     <mergeCell ref="C459:C462"/>
+    <mergeCell ref="D459:D462"/>
     <mergeCell ref="A463:A473"/>
     <mergeCell ref="B463:B473"/>
     <mergeCell ref="C463:C473"/>
+    <mergeCell ref="D463:D473"/>
     <mergeCell ref="A474:A482"/>
     <mergeCell ref="B474:B482"/>
     <mergeCell ref="C474:C482"/>
+    <mergeCell ref="D474:D482"/>
     <mergeCell ref="A483:A488"/>
     <mergeCell ref="B483:B488"/>
     <mergeCell ref="C483:C488"/>
+    <mergeCell ref="D483:D488"/>
     <mergeCell ref="A489:A498"/>
     <mergeCell ref="B489:B498"/>
     <mergeCell ref="C489:C498"/>
+    <mergeCell ref="D489:D498"/>
     <mergeCell ref="A499:A504"/>
     <mergeCell ref="B499:B504"/>
     <mergeCell ref="C499:C504"/>
+    <mergeCell ref="D499:D504"/>
     <mergeCell ref="A505:A516"/>
     <mergeCell ref="B505:B516"/>
     <mergeCell ref="C505:C516"/>
+    <mergeCell ref="D505:D516"/>
     <mergeCell ref="A517:A526"/>
     <mergeCell ref="B517:B526"/>
     <mergeCell ref="C517:C526"/>
+    <mergeCell ref="D517:D526"/>
     <mergeCell ref="A527:A532"/>
     <mergeCell ref="B527:B532"/>
     <mergeCell ref="C527:C532"/>
+    <mergeCell ref="D527:D532"/>
     <mergeCell ref="A533:A537"/>
     <mergeCell ref="B533:B537"/>
     <mergeCell ref="C533:C537"/>
+    <mergeCell ref="D533:D537"/>
     <mergeCell ref="A538:A554"/>
     <mergeCell ref="B538:B554"/>
     <mergeCell ref="C538:C554"/>
+    <mergeCell ref="D538:D554"/>
     <mergeCell ref="A555:A565"/>
     <mergeCell ref="B555:B565"/>
     <mergeCell ref="C555:C565"/>
+    <mergeCell ref="D555:D565"/>
     <mergeCell ref="A566:A571"/>
     <mergeCell ref="B566:B571"/>
     <mergeCell ref="C566:C571"/>
+    <mergeCell ref="D566:D571"/>
     <mergeCell ref="A572:A576"/>
     <mergeCell ref="B572:B576"/>
     <mergeCell ref="C572:C576"/>
+    <mergeCell ref="D572:D576"/>
     <mergeCell ref="A577:A596"/>
     <mergeCell ref="B577:B596"/>
     <mergeCell ref="C577:C596"/>
+    <mergeCell ref="D577:D596"/>
     <mergeCell ref="A597:A616"/>
     <mergeCell ref="B597:B616"/>
     <mergeCell ref="C597:C616"/>
+    <mergeCell ref="D597:D616"/>
     <mergeCell ref="A617:A636"/>
     <mergeCell ref="B617:B636"/>
     <mergeCell ref="C617:C636"/>
+    <mergeCell ref="D617:D636"/>
     <mergeCell ref="A637:A656"/>
     <mergeCell ref="B637:B656"/>
     <mergeCell ref="C637:C656"/>
+    <mergeCell ref="D637:D656"/>
     <mergeCell ref="A657:A676"/>
     <mergeCell ref="B657:B676"/>
     <mergeCell ref="C657:C676"/>
+    <mergeCell ref="D657:D676"/>
     <mergeCell ref="A677:A696"/>
     <mergeCell ref="B677:B696"/>
     <mergeCell ref="C677:C696"/>
+    <mergeCell ref="D677:D696"/>
   </mergeCells>
   <printOptions gridLines="1" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
